--- a/Santa Cruz V2/listas/bola_parada_especialistas.xlsx
+++ b/Santa Cruz V2/listas/bola_parada_especialistas.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1315" uniqueCount="439">
   <si>
     <t>liga</t>
   </si>
@@ -77,6 +77,18 @@
     <t>escanteios_2025</t>
   </si>
   <si>
+    <t>assist_bp_2026</t>
+  </si>
+  <si>
+    <t>assist_bp_3t</t>
+  </si>
+  <si>
+    <t>assist_escanteio_3t</t>
+  </si>
+  <si>
+    <t>gols_falta_direta_3t</t>
+  </si>
+  <si>
     <t>Série B</t>
   </si>
   <si>
@@ -294,6 +306,18 @@
   </si>
   <si>
     <t>gols_cabeca_2025</t>
+  </si>
+  <si>
+    <t>gols_bp_2026</t>
+  </si>
+  <si>
+    <t>gols_bp_3t</t>
+  </si>
+  <si>
+    <t>gols_bp_cabeca_3t</t>
+  </si>
+  <si>
+    <t>xg_bp_3t</t>
   </si>
   <si>
     <t>ZE</t>
@@ -1671,10 +1695,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1729,19 +1753,31 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E2">
         <v>33</v>
@@ -1750,13 +1786,13 @@
         <v>1477</v>
       </c>
       <c r="G2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H2">
         <v>800000</v>
       </c>
       <c r="I2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J2">
         <v>96.5</v>
@@ -1779,19 +1815,31 @@
       <c r="P2">
         <v>43.8</v>
       </c>
-    </row>
-    <row r="3" spans="1:18">
+      <c r="S2">
+        <v>2</v>
+      </c>
+      <c r="T2">
+        <v>4</v>
+      </c>
+      <c r="U2">
+        <v>3</v>
+      </c>
+      <c r="V2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E3">
         <v>33</v>
@@ -1800,13 +1848,13 @@
         <v>1987</v>
       </c>
       <c r="G3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H3">
         <v>600000</v>
       </c>
       <c r="I3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J3">
         <v>95.90000000000001</v>
@@ -1835,19 +1883,31 @@
       <c r="R3">
         <v>105</v>
       </c>
-    </row>
-    <row r="4" spans="1:18">
+      <c r="S3">
+        <v>4</v>
+      </c>
+      <c r="T3">
+        <v>9</v>
+      </c>
+      <c r="U3">
+        <v>5</v>
+      </c>
+      <c r="V3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E4">
         <v>26</v>
@@ -1856,10 +1916,10 @@
         <v>2106</v>
       </c>
       <c r="G4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J4">
         <v>95.2</v>
@@ -1882,19 +1942,31 @@
       <c r="P4">
         <v>64.3</v>
       </c>
-    </row>
-    <row r="5" spans="1:18">
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E5">
         <v>24</v>
@@ -1903,10 +1975,10 @@
         <v>2289</v>
       </c>
       <c r="G5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I5" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J5">
         <v>92.7</v>
@@ -1935,19 +2007,31 @@
       <c r="R5">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:18">
+      <c r="S5">
+        <v>3</v>
+      </c>
+      <c r="T5">
+        <v>4</v>
+      </c>
+      <c r="U5">
+        <v>2</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E6">
         <v>26</v>
@@ -1956,10 +2040,10 @@
         <v>1103</v>
       </c>
       <c r="G6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J6">
         <v>92</v>
@@ -1982,19 +2066,31 @@
       <c r="P6">
         <v>38.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E7">
         <v>25</v>
@@ -2003,10 +2099,10 @@
         <v>1516</v>
       </c>
       <c r="G7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J7">
         <v>91.7</v>
@@ -2035,19 +2131,31 @@
       <c r="R7">
         <v>76</v>
       </c>
-    </row>
-    <row r="8" spans="1:18">
+      <c r="S7">
+        <v>2</v>
+      </c>
+      <c r="T7">
+        <v>5</v>
+      </c>
+      <c r="U7">
+        <v>4</v>
+      </c>
+      <c r="V7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E8">
         <v>28</v>
@@ -2056,10 +2164,10 @@
         <v>1571</v>
       </c>
       <c r="G8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I8" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J8">
         <v>91.2</v>
@@ -2082,19 +2190,31 @@
       <c r="P8">
         <v>35.7</v>
       </c>
-    </row>
-    <row r="9" spans="1:18">
+      <c r="S8">
+        <v>3</v>
+      </c>
+      <c r="T8">
+        <v>3</v>
+      </c>
+      <c r="U8">
+        <v>2</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E9">
         <v>23</v>
@@ -2103,10 +2223,10 @@
         <v>1303</v>
       </c>
       <c r="G9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I9" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J9">
         <v>90.40000000000001</v>
@@ -2129,19 +2249,31 @@
       <c r="P9">
         <v>38.7</v>
       </c>
-    </row>
-    <row r="10" spans="1:18">
+      <c r="S9">
+        <v>2</v>
+      </c>
+      <c r="T9">
+        <v>2</v>
+      </c>
+      <c r="U9">
+        <v>2</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E10">
         <v>23</v>
@@ -2150,10 +2282,10 @@
         <v>1011</v>
       </c>
       <c r="G10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I10" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J10">
         <v>90.2</v>
@@ -2176,19 +2308,31 @@
       <c r="P10">
         <v>33.3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18">
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E11">
         <v>25</v>
@@ -2197,10 +2341,10 @@
         <v>1991</v>
       </c>
       <c r="G11" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J11">
         <v>90.09999999999999</v>
@@ -2223,19 +2367,31 @@
       <c r="P11">
         <v>41.8</v>
       </c>
-    </row>
-    <row r="12" spans="1:18">
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>2</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E12">
         <v>28</v>
@@ -2244,10 +2400,10 @@
         <v>1838</v>
       </c>
       <c r="G12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I12" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J12">
         <v>89.5</v>
@@ -2276,19 +2432,31 @@
       <c r="R12">
         <v>67</v>
       </c>
-    </row>
-    <row r="13" spans="1:18">
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E13">
         <v>30</v>
@@ -2297,10 +2465,10 @@
         <v>2396</v>
       </c>
       <c r="G13" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I13" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J13">
         <v>89</v>
@@ -2329,19 +2497,31 @@
       <c r="R13">
         <v>102</v>
       </c>
-    </row>
-    <row r="14" spans="1:18">
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>4</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E14">
         <v>27</v>
@@ -2350,13 +2530,13 @@
         <v>1313</v>
       </c>
       <c r="G14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H14">
         <v>750000</v>
       </c>
       <c r="I14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J14">
         <v>88.90000000000001</v>
@@ -2379,19 +2559,31 @@
       <c r="P14">
         <v>44.4</v>
       </c>
-    </row>
-    <row r="15" spans="1:18">
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E15">
         <v>20</v>
@@ -2400,10 +2592,10 @@
         <v>1761</v>
       </c>
       <c r="G15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I15" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J15">
         <v>88</v>
@@ -2426,19 +2618,31 @@
       <c r="P15">
         <v>30.2</v>
       </c>
-    </row>
-    <row r="16" spans="1:18">
+      <c r="S15">
+        <v>3</v>
+      </c>
+      <c r="T15">
+        <v>3</v>
+      </c>
+      <c r="U15">
+        <v>3</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E16">
         <v>32</v>
@@ -2447,13 +2651,13 @@
         <v>1569</v>
       </c>
       <c r="G16" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H16">
         <v>500000</v>
       </c>
       <c r="I16" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J16">
         <v>87.59999999999999</v>
@@ -2482,19 +2686,31 @@
       <c r="R16">
         <v>18</v>
       </c>
-    </row>
-    <row r="17" spans="1:18">
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>5</v>
+      </c>
+      <c r="U16">
+        <v>3</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E17">
         <v>24</v>
@@ -2503,10 +2719,10 @@
         <v>2186</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I17" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J17">
         <v>86.7</v>
@@ -2535,19 +2751,31 @@
       <c r="R17">
         <v>66</v>
       </c>
-    </row>
-    <row r="18" spans="1:18">
+      <c r="S17">
+        <v>3</v>
+      </c>
+      <c r="T17">
+        <v>3</v>
+      </c>
+      <c r="U17">
+        <v>2</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E18">
         <v>29</v>
@@ -2556,13 +2784,13 @@
         <v>2301</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H18">
         <v>125000</v>
       </c>
       <c r="I18" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="J18">
         <v>84.5</v>
@@ -2591,19 +2819,31 @@
       <c r="R18">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:18">
+      <c r="S18">
+        <v>2</v>
+      </c>
+      <c r="T18">
+        <v>2</v>
+      </c>
+      <c r="U18">
+        <v>2</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E19">
         <v>29</v>
@@ -2612,13 +2852,13 @@
         <v>1941</v>
       </c>
       <c r="G19" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H19">
         <v>900000</v>
       </c>
       <c r="I19" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J19">
         <v>84.2</v>
@@ -2641,19 +2881,31 @@
       <c r="P19">
         <v>48.3</v>
       </c>
-    </row>
-    <row r="20" spans="1:18">
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E20">
         <v>29</v>
@@ -2662,13 +2914,13 @@
         <v>1435</v>
       </c>
       <c r="G20" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H20">
         <v>1000000</v>
       </c>
       <c r="I20" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J20">
         <v>84.2</v>
@@ -2691,19 +2943,31 @@
       <c r="P20">
         <v>36.4</v>
       </c>
-    </row>
-    <row r="21" spans="1:18">
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>3</v>
+      </c>
+      <c r="U20">
+        <v>2</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E21">
         <v>32</v>
@@ -2712,13 +2976,13 @@
         <v>1015</v>
       </c>
       <c r="G21" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H21">
         <v>200000</v>
       </c>
       <c r="I21" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J21">
         <v>83.90000000000001</v>
@@ -2747,19 +3011,31 @@
       <c r="R21">
         <v>97</v>
       </c>
-    </row>
-    <row r="22" spans="1:18">
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>2</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D22" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E22">
         <v>26</v>
@@ -2768,13 +3044,13 @@
         <v>1877</v>
       </c>
       <c r="G22" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H22">
         <v>400000</v>
       </c>
       <c r="I22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J22">
         <v>83.09999999999999</v>
@@ -2797,19 +3073,31 @@
       <c r="P22">
         <v>40</v>
       </c>
-    </row>
-    <row r="23" spans="1:18">
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E23">
         <v>31</v>
@@ -2818,13 +3106,13 @@
         <v>1972</v>
       </c>
       <c r="G23" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H23">
         <v>250000</v>
       </c>
       <c r="I23" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J23">
         <v>83.09999999999999</v>
@@ -2847,19 +3135,31 @@
       <c r="P23">
         <v>28.1</v>
       </c>
-    </row>
-    <row r="24" spans="1:18">
+      <c r="S23">
+        <v>1</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E24">
         <v>29</v>
@@ -2868,10 +3168,10 @@
         <v>2285</v>
       </c>
       <c r="G24" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I24" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J24">
         <v>81.8</v>
@@ -2900,19 +3200,31 @@
       <c r="R24">
         <v>17</v>
       </c>
-    </row>
-    <row r="25" spans="1:18">
+      <c r="S24">
+        <v>2</v>
+      </c>
+      <c r="T24">
+        <v>2</v>
+      </c>
+      <c r="U24">
+        <v>2</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D25" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E25">
         <v>31</v>
@@ -2921,13 +3233,13 @@
         <v>1133</v>
       </c>
       <c r="G25" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H25">
         <v>1000000</v>
       </c>
       <c r="I25" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J25">
         <v>81.09999999999999</v>
@@ -2956,19 +3268,31 @@
       <c r="R25">
         <v>21</v>
       </c>
-    </row>
-    <row r="26" spans="1:18">
+      <c r="S25">
+        <v>1</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+      <c r="U25">
+        <v>1</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -2977,13 +3301,13 @@
         <v>2014</v>
       </c>
       <c r="G26" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H26">
         <v>750000</v>
       </c>
       <c r="I26" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J26">
         <v>79.90000000000001</v>
@@ -3005,6 +3329,18 @@
       </c>
       <c r="P26">
         <v>29.8</v>
+      </c>
+      <c r="S26">
+        <v>1</v>
+      </c>
+      <c r="T26">
+        <v>1</v>
+      </c>
+      <c r="U26">
+        <v>1</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3014,10 +3350,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3046,42 +3382,54 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17">
+        <v>94</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E2">
         <v>33</v>
@@ -3090,13 +3438,13 @@
         <v>1988</v>
       </c>
       <c r="G2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H2">
         <v>900000</v>
       </c>
       <c r="I2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J2">
         <v>92.5</v>
@@ -3116,19 +3464,31 @@
       <c r="O2">
         <v>194</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2">
+        <v>2</v>
+      </c>
+      <c r="S2">
+        <v>5</v>
+      </c>
+      <c r="T2">
+        <v>4</v>
+      </c>
+      <c r="U2">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E3">
         <v>26</v>
@@ -3137,10 +3497,10 @@
         <v>2612</v>
       </c>
       <c r="G3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J3">
         <v>90.7</v>
@@ -3166,19 +3526,31 @@
       <c r="Q3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3">
+        <v>3</v>
+      </c>
+      <c r="S3">
+        <v>4</v>
+      </c>
+      <c r="T3">
+        <v>3</v>
+      </c>
+      <c r="U3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E4">
         <v>29</v>
@@ -3187,13 +3559,13 @@
         <v>2542</v>
       </c>
       <c r="G4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H4">
         <v>2000000</v>
       </c>
       <c r="I4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J4">
         <v>88.5</v>
@@ -3213,19 +3585,31 @@
       <c r="O4">
         <v>187</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4">
+        <v>2</v>
+      </c>
+      <c r="S4">
+        <v>4</v>
+      </c>
+      <c r="T4">
+        <v>2</v>
+      </c>
+      <c r="U4">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E5">
         <v>31</v>
@@ -3234,13 +3618,13 @@
         <v>1585</v>
       </c>
       <c r="G5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H5">
         <v>400000</v>
       </c>
       <c r="I5" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J5">
         <v>88.3</v>
@@ -3266,19 +3650,31 @@
       <c r="Q5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5">
+        <v>2</v>
+      </c>
+      <c r="S5">
+        <v>2</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E6">
         <v>28</v>
@@ -3287,13 +3683,13 @@
         <v>1299</v>
       </c>
       <c r="G6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H6">
         <v>800000</v>
       </c>
       <c r="I6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J6">
         <v>88</v>
@@ -3313,19 +3709,31 @@
       <c r="O6">
         <v>187</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6">
+        <v>2</v>
+      </c>
+      <c r="S6">
+        <v>2</v>
+      </c>
+      <c r="T6">
+        <v>2</v>
+      </c>
+      <c r="U6">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E7">
         <v>23</v>
@@ -3334,10 +3742,10 @@
         <v>2039</v>
       </c>
       <c r="G7" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J7">
         <v>85</v>
@@ -3357,19 +3765,31 @@
       <c r="O7">
         <v>190</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E8">
         <v>31</v>
@@ -3378,13 +3798,13 @@
         <v>1645</v>
       </c>
       <c r="G8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H8">
         <v>600000</v>
       </c>
       <c r="I8" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J8">
         <v>84.09999999999999</v>
@@ -3410,19 +3830,31 @@
       <c r="Q8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>3</v>
+      </c>
+      <c r="T8">
+        <v>3</v>
+      </c>
+      <c r="U8">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E9">
         <v>24</v>
@@ -3431,10 +3863,10 @@
         <v>1685</v>
       </c>
       <c r="G9" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="I9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J9">
         <v>84.09999999999999</v>
@@ -3454,19 +3886,31 @@
       <c r="O9">
         <v>180</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="R9">
+        <v>3</v>
+      </c>
+      <c r="S9">
+        <v>3</v>
+      </c>
+      <c r="T9">
+        <v>2</v>
+      </c>
+      <c r="U9">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E10">
         <v>29</v>
@@ -3475,10 +3919,10 @@
         <v>1236</v>
       </c>
       <c r="G10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I10" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J10">
         <v>83.09999999999999</v>
@@ -3501,19 +3945,31 @@
       <c r="Q10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E11">
         <v>24</v>
@@ -3522,10 +3978,10 @@
         <v>1348</v>
       </c>
       <c r="G11" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="I11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J11">
         <v>82.09999999999999</v>
@@ -3542,19 +3998,31 @@
       <c r="N11">
         <v>40</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="R11">
+        <v>2</v>
+      </c>
+      <c r="S11">
+        <v>2</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E12">
         <v>27</v>
@@ -3563,13 +4031,13 @@
         <v>2236</v>
       </c>
       <c r="G12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H12">
         <v>300000</v>
       </c>
       <c r="I12" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J12">
         <v>80.8</v>
@@ -3595,19 +4063,31 @@
       <c r="Q12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="R12">
+        <v>3</v>
+      </c>
+      <c r="S12">
+        <v>4</v>
+      </c>
+      <c r="T12">
+        <v>3</v>
+      </c>
+      <c r="U12">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E13">
         <v>22</v>
@@ -3616,10 +4096,10 @@
         <v>1515</v>
       </c>
       <c r="G13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I13" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J13">
         <v>80.40000000000001</v>
@@ -3639,19 +4119,31 @@
       <c r="O13">
         <v>184</v>
       </c>
-    </row>
-    <row r="14" spans="1:17">
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E14">
         <v>28</v>
@@ -3660,13 +4152,13 @@
         <v>2420</v>
       </c>
       <c r="G14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H14">
         <v>400000</v>
       </c>
       <c r="I14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J14">
         <v>79.90000000000001</v>
@@ -3686,19 +4178,31 @@
       <c r="O14">
         <v>185</v>
       </c>
-    </row>
-    <row r="15" spans="1:17">
+      <c r="R14">
+        <v>5</v>
+      </c>
+      <c r="S14">
+        <v>5</v>
+      </c>
+      <c r="T14">
+        <v>3</v>
+      </c>
+      <c r="U14">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E15">
         <v>30</v>
@@ -3707,10 +4211,10 @@
         <v>1009</v>
       </c>
       <c r="G15" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I15" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J15">
         <v>79.8</v>
@@ -3730,19 +4234,31 @@
       <c r="O15">
         <v>186</v>
       </c>
-    </row>
-    <row r="16" spans="1:17">
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E16">
         <v>29</v>
@@ -3751,13 +4267,13 @@
         <v>1539</v>
       </c>
       <c r="G16" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H16">
         <v>75000</v>
       </c>
       <c r="I16" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J16">
         <v>78.2</v>
@@ -3777,19 +4293,31 @@
       <c r="O16">
         <v>185</v>
       </c>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E17">
         <v>30</v>
@@ -3798,10 +4326,10 @@
         <v>1733</v>
       </c>
       <c r="G17" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I17" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J17">
         <v>77.7</v>
@@ -3827,19 +4355,31 @@
       <c r="Q17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E18">
         <v>22</v>
@@ -3848,10 +4388,10 @@
         <v>1877</v>
       </c>
       <c r="G18" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I18" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J18">
         <v>77.40000000000001</v>
@@ -3877,19 +4417,31 @@
       <c r="Q18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="R18">
+        <v>2</v>
+      </c>
+      <c r="S18">
+        <v>3</v>
+      </c>
+      <c r="T18">
+        <v>3</v>
+      </c>
+      <c r="U18">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E19">
         <v>27</v>
@@ -3898,10 +4450,10 @@
         <v>1800</v>
       </c>
       <c r="G19" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I19" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J19">
         <v>76.40000000000001</v>
@@ -3921,19 +4473,31 @@
       <c r="O19">
         <v>182</v>
       </c>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E20">
         <v>25</v>
@@ -3942,13 +4506,13 @@
         <v>1104</v>
       </c>
       <c r="G20" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H20">
         <v>400000</v>
       </c>
       <c r="I20" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J20">
         <v>75.59999999999999</v>
@@ -3968,19 +4532,31 @@
       <c r="O20">
         <v>180</v>
       </c>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="R20">
+        <v>2</v>
+      </c>
+      <c r="S20">
+        <v>2</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E21">
         <v>31</v>
@@ -3989,10 +4565,10 @@
         <v>1438</v>
       </c>
       <c r="G21" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I21" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J21">
         <v>74.8</v>
@@ -4018,19 +4594,31 @@
       <c r="Q21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:17">
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>2</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="E22">
         <v>29</v>
@@ -4039,13 +4627,13 @@
         <v>908</v>
       </c>
       <c r="G22" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H22">
         <v>250000</v>
       </c>
       <c r="I22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J22">
         <v>72.90000000000001</v>
@@ -4065,19 +4653,31 @@
       <c r="O22">
         <v>181</v>
       </c>
-    </row>
-    <row r="23" spans="1:17">
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E23">
         <v>28</v>
@@ -4086,13 +4686,13 @@
         <v>2493</v>
       </c>
       <c r="G23" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H23">
         <v>1200000</v>
       </c>
       <c r="I23" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J23">
         <v>72.90000000000001</v>
@@ -4112,19 +4712,31 @@
       <c r="O23">
         <v>186</v>
       </c>
-    </row>
-    <row r="24" spans="1:17">
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>2</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+      <c r="U23">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E24">
         <v>29</v>
@@ -4133,13 +4745,13 @@
         <v>2301</v>
       </c>
       <c r="G24" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H24">
         <v>125000</v>
       </c>
       <c r="I24" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="J24">
         <v>72.09999999999999</v>
@@ -4165,19 +4777,31 @@
       <c r="Q24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:17">
+      <c r="R24">
+        <v>3</v>
+      </c>
+      <c r="S24">
+        <v>3</v>
+      </c>
+      <c r="T24">
+        <v>2</v>
+      </c>
+      <c r="U24">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D25" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E25">
         <v>28</v>
@@ -4186,13 +4810,13 @@
         <v>960</v>
       </c>
       <c r="G25" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H25">
         <v>500000</v>
       </c>
       <c r="I25" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J25">
         <v>71.5</v>
@@ -4218,19 +4842,31 @@
       <c r="Q25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:17">
+      <c r="R25">
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <v>2</v>
+      </c>
+      <c r="T25">
+        <v>2</v>
+      </c>
+      <c r="U25">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D26" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E26">
         <v>27</v>
@@ -4239,10 +4875,10 @@
         <v>1728</v>
       </c>
       <c r="G26" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I26" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J26">
         <v>69.90000000000001</v>
@@ -4267,6 +4903,18 @@
       </c>
       <c r="Q26">
         <v>2</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>1</v>
+      </c>
+      <c r="T26">
+        <v>1</v>
+      </c>
+      <c r="U26">
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
@@ -4331,16 +4979,16 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="E2">
         <v>28</v>
@@ -4349,13 +4997,13 @@
         <v>1682</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="J2">
         <v>96.2</v>
@@ -4381,16 +5029,16 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E3">
         <v>30</v>
@@ -4399,13 +5047,13 @@
         <v>1920</v>
       </c>
       <c r="G3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="J3">
         <v>95.3</v>
@@ -4431,16 +5079,16 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E4">
         <v>26</v>
@@ -4449,13 +5097,13 @@
         <v>1035</v>
       </c>
       <c r="G4" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="H4">
         <v>9000000</v>
       </c>
       <c r="I4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J4">
         <v>94.5</v>
@@ -4481,16 +5129,16 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E5">
         <v>32</v>
@@ -4499,13 +5147,13 @@
         <v>1061</v>
       </c>
       <c r="G5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="J5">
         <v>94</v>
@@ -4531,16 +5179,16 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D6" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="E6">
         <v>31</v>
@@ -4549,13 +5197,13 @@
         <v>980</v>
       </c>
       <c r="G6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J6">
         <v>92.3</v>
@@ -4581,16 +5229,16 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D7" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="E7">
         <v>30</v>
@@ -4599,13 +5247,13 @@
         <v>1914</v>
       </c>
       <c r="G7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="J7">
         <v>92.3</v>
@@ -4631,16 +5279,16 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="D8" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E8">
         <v>33</v>
@@ -4649,13 +5297,13 @@
         <v>1760</v>
       </c>
       <c r="G8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H8">
         <v>6000000</v>
       </c>
       <c r="I8" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J8">
         <v>92.2</v>
@@ -4681,16 +5329,16 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E9">
         <v>30</v>
@@ -4699,13 +5347,13 @@
         <v>1732</v>
       </c>
       <c r="G9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H9">
         <v>4500000</v>
       </c>
       <c r="I9" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="J9">
         <v>90.8</v>
@@ -4731,16 +5379,16 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E10">
         <v>28</v>
@@ -4749,13 +5397,13 @@
         <v>1424</v>
       </c>
       <c r="G10" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H10">
         <v>11000000</v>
       </c>
       <c r="I10" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J10">
         <v>89.7</v>
@@ -4781,16 +5429,16 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D11" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E11">
         <v>26</v>
@@ -4799,13 +5447,13 @@
         <v>1736</v>
       </c>
       <c r="G11" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J11">
         <v>88.8</v>
@@ -4831,16 +5479,16 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D12" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E12">
         <v>24</v>
@@ -4849,13 +5497,13 @@
         <v>1456</v>
       </c>
       <c r="G12" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J12">
         <v>87.40000000000001</v>
@@ -4881,16 +5529,16 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D13" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="E13">
         <v>29</v>
@@ -4899,13 +5547,13 @@
         <v>1281</v>
       </c>
       <c r="G13" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H13">
         <v>5000000</v>
       </c>
       <c r="I13" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="J13">
         <v>86.8</v>
@@ -4931,16 +5579,16 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D14" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E14">
         <v>19</v>
@@ -4949,13 +5597,13 @@
         <v>933</v>
       </c>
       <c r="G14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J14">
         <v>85.2</v>
@@ -4981,16 +5629,16 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="D15" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="E15">
         <v>23</v>
@@ -4999,13 +5647,13 @@
         <v>934</v>
       </c>
       <c r="G15" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J15">
         <v>83.8</v>
@@ -5031,16 +5679,16 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D16" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="E16">
         <v>28</v>
@@ -5049,13 +5697,13 @@
         <v>1433</v>
       </c>
       <c r="G16" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H16">
         <v>1500000</v>
       </c>
       <c r="I16" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J16">
         <v>83.7</v>
@@ -5081,16 +5729,16 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D17" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E17">
         <v>33</v>
@@ -5099,13 +5747,13 @@
         <v>1103</v>
       </c>
       <c r="G17" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H17">
         <v>2500000</v>
       </c>
       <c r="I17" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="J17">
         <v>83.2</v>
@@ -5131,16 +5779,16 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="D18" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="E18">
         <v>26</v>
@@ -5149,13 +5797,13 @@
         <v>1379</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H18">
         <v>5000000</v>
       </c>
       <c r="I18" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="J18">
         <v>82.90000000000001</v>
@@ -5181,16 +5829,16 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="D19" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E19">
         <v>29</v>
@@ -5199,13 +5847,13 @@
         <v>1916</v>
       </c>
       <c r="G19" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H19">
         <v>3000000</v>
       </c>
       <c r="I19" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J19">
         <v>81.40000000000001</v>
@@ -5231,16 +5879,16 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="D20" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="E20">
         <v>28</v>
@@ -5249,13 +5897,13 @@
         <v>1691</v>
       </c>
       <c r="G20" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H20">
         <v>1200000</v>
       </c>
       <c r="I20" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J20">
         <v>81</v>
@@ -5281,16 +5929,16 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D21" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="E21">
         <v>27</v>
@@ -5299,13 +5947,13 @@
         <v>1005</v>
       </c>
       <c r="G21" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H21">
         <v>1000000</v>
       </c>
       <c r="I21" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="J21">
         <v>80.7</v>
@@ -5331,16 +5979,16 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D22" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="E22">
         <v>32</v>
@@ -5349,13 +5997,13 @@
         <v>1315</v>
       </c>
       <c r="G22" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="J22">
         <v>80.59999999999999</v>
@@ -5381,16 +6029,16 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D23" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="E23">
         <v>26</v>
@@ -5399,13 +6047,13 @@
         <v>907</v>
       </c>
       <c r="G23" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H23">
         <v>450000</v>
       </c>
       <c r="I23" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J23">
         <v>80.40000000000001</v>
@@ -5431,16 +6079,16 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="D24" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E24">
         <v>27</v>
@@ -5449,13 +6097,13 @@
         <v>948</v>
       </c>
       <c r="G24" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="J24">
         <v>79.3</v>
@@ -5481,16 +6129,16 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D25" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E25">
         <v>28</v>
@@ -5499,13 +6147,13 @@
         <v>957</v>
       </c>
       <c r="G25" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J25">
         <v>78.7</v>
@@ -5531,16 +6179,16 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="D26" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E26">
         <v>26</v>
@@ -5549,13 +6197,13 @@
         <v>1526</v>
       </c>
       <c r="G26" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H26">
         <v>3000000</v>
       </c>
       <c r="I26" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J26">
         <v>78.09999999999999</v>
@@ -5618,36 +6266,36 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E2">
         <v>31</v>
@@ -5656,13 +6304,13 @@
         <v>1633</v>
       </c>
       <c r="G2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H2">
         <v>1000000</v>
       </c>
       <c r="I2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J2">
         <v>96.8</v>
@@ -5685,16 +6333,16 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="E3">
         <v>28</v>
@@ -5703,13 +6351,13 @@
         <v>2261</v>
       </c>
       <c r="G3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H3">
         <v>250000</v>
       </c>
       <c r="I3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J3">
         <v>93.59999999999999</v>
@@ -5732,16 +6380,16 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="D4" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="E4">
         <v>29</v>
@@ -5750,13 +6398,13 @@
         <v>920</v>
       </c>
       <c r="G4" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H4">
         <v>1500000</v>
       </c>
       <c r="I4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J4">
         <v>93.59999999999999</v>
@@ -5779,16 +6427,16 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E5">
         <v>33</v>
@@ -5797,13 +6445,13 @@
         <v>1975</v>
       </c>
       <c r="G5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H5">
         <v>7500000</v>
       </c>
       <c r="I5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J5">
         <v>91.2</v>
@@ -5826,16 +6474,16 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D6" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="E6">
         <v>22</v>
@@ -5844,13 +6492,13 @@
         <v>1549</v>
       </c>
       <c r="G6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H6">
         <v>400000</v>
       </c>
       <c r="I6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J6">
         <v>90.5</v>
@@ -5873,16 +6521,16 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="D7" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E7">
         <v>30</v>
@@ -5891,13 +6539,13 @@
         <v>1232</v>
       </c>
       <c r="G7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H7">
         <v>3500000</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J7">
         <v>89</v>
@@ -5920,16 +6568,16 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="D8" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E8">
         <v>31</v>
@@ -5938,13 +6586,13 @@
         <v>1445</v>
       </c>
       <c r="G8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H8">
         <v>2500000</v>
       </c>
       <c r="I8" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="J8">
         <v>88.8</v>
@@ -5967,16 +6615,16 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="D9" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E9">
         <v>27</v>
@@ -5985,13 +6633,13 @@
         <v>1875</v>
       </c>
       <c r="G9" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="H9">
         <v>2500000</v>
       </c>
       <c r="I9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J9">
         <v>87.8</v>
@@ -6014,16 +6662,16 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="D10" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="E10">
         <v>29</v>
@@ -6032,13 +6680,13 @@
         <v>1694</v>
       </c>
       <c r="G10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H10">
         <v>100000</v>
       </c>
       <c r="I10" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J10">
         <v>85.59999999999999</v>
@@ -6061,16 +6709,16 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="E11">
         <v>22</v>
@@ -6079,13 +6727,13 @@
         <v>1435</v>
       </c>
       <c r="G11" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J11">
         <v>85.59999999999999</v>
@@ -6108,16 +6756,16 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D12" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="E12">
         <v>29</v>
@@ -6126,13 +6774,13 @@
         <v>1711</v>
       </c>
       <c r="G12" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H12">
         <v>100000</v>
       </c>
       <c r="I12" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J12">
         <v>85.5</v>
@@ -6155,16 +6803,16 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D13" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E13">
         <v>32</v>
@@ -6173,13 +6821,13 @@
         <v>1877</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H13">
         <v>3500000</v>
       </c>
       <c r="I13" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="J13">
         <v>85.2</v>
@@ -6202,16 +6850,16 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E14">
         <v>27</v>
@@ -6220,13 +6868,13 @@
         <v>1480</v>
       </c>
       <c r="G14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H14">
         <v>3500000</v>
       </c>
       <c r="I14" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="J14">
         <v>84.90000000000001</v>
@@ -6249,16 +6897,16 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="D15" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E15">
         <v>29</v>
@@ -6267,13 +6915,13 @@
         <v>2000</v>
       </c>
       <c r="G15" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H15">
         <v>10000000</v>
       </c>
       <c r="I15" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J15">
         <v>84.8</v>
@@ -6296,16 +6944,16 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E16">
         <v>29</v>
@@ -6314,13 +6962,13 @@
         <v>1708</v>
       </c>
       <c r="G16" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H16">
         <v>850000</v>
       </c>
       <c r="I16" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J16">
         <v>83.90000000000001</v>
@@ -6343,16 +6991,16 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="D17" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E17">
         <v>30</v>
@@ -6361,13 +7009,13 @@
         <v>1618</v>
       </c>
       <c r="G17" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J17">
         <v>83.7</v>
@@ -6390,16 +7038,16 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="D18" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E18">
         <v>21</v>
@@ -6408,13 +7056,13 @@
         <v>1323</v>
       </c>
       <c r="G18" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J18">
         <v>82.3</v>
@@ -6437,16 +7085,16 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D19" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E19">
         <v>31</v>
@@ -6455,13 +7103,13 @@
         <v>1909</v>
       </c>
       <c r="G19" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H19">
         <v>4000000</v>
       </c>
       <c r="I19" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J19">
         <v>82.09999999999999</v>
@@ -6484,16 +7132,16 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D20" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E20">
         <v>25</v>
@@ -6502,13 +7150,13 @@
         <v>1622</v>
       </c>
       <c r="G20" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J20">
         <v>80.3</v>
@@ -6531,16 +7179,16 @@
     </row>
     <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="D21" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E21">
         <v>25</v>
@@ -6549,13 +7197,13 @@
         <v>2021</v>
       </c>
       <c r="G21" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H21">
         <v>2000000</v>
       </c>
       <c r="I21" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J21">
         <v>78.90000000000001</v>
@@ -6578,16 +7226,16 @@
     </row>
     <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C22" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D22" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="E22">
         <v>27</v>
@@ -6596,13 +7244,13 @@
         <v>1931</v>
       </c>
       <c r="G22" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H22">
         <v>250000</v>
       </c>
       <c r="I22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J22">
         <v>78.7</v>
@@ -6625,16 +7273,16 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D23" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -6643,13 +7291,13 @@
         <v>1184</v>
       </c>
       <c r="G23" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J23">
         <v>77.3</v>
@@ -6672,16 +7320,16 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D24" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E24">
         <v>27</v>
@@ -6690,13 +7338,13 @@
         <v>1518</v>
       </c>
       <c r="G24" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H24">
         <v>4000000</v>
       </c>
       <c r="I24" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J24">
         <v>76.7</v>
@@ -6719,16 +7367,16 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D25" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E25">
         <v>29</v>
@@ -6737,13 +7385,13 @@
         <v>1082</v>
       </c>
       <c r="G25" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J25">
         <v>76.5</v>
@@ -6766,16 +7414,16 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="D26" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E26">
         <v>29</v>
@@ -6784,13 +7432,13 @@
         <v>1916</v>
       </c>
       <c r="G26" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H26">
         <v>3000000</v>
       </c>
       <c r="I26" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J26">
         <v>76.09999999999999</v>
@@ -6873,16 +7521,16 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="D2" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="E2">
         <v>27</v>
@@ -6891,13 +7539,13 @@
         <v>962</v>
       </c>
       <c r="G2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H2">
         <v>7500000</v>
       </c>
       <c r="I2" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="J2">
         <v>97.5</v>
@@ -6923,16 +7571,16 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="D3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E3">
         <v>19</v>
@@ -6941,13 +7589,13 @@
         <v>1422</v>
       </c>
       <c r="G3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J3">
         <v>96.3</v>
@@ -6973,16 +7621,16 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="D4" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="E4">
         <v>31</v>
@@ -6994,7 +7642,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J4">
         <v>96</v>
@@ -7020,16 +7668,16 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="E5">
         <v>32</v>
@@ -7038,13 +7686,13 @@
         <v>939</v>
       </c>
       <c r="G5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H5">
         <v>175000</v>
       </c>
       <c r="I5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J5">
         <v>96</v>
@@ -7070,16 +7718,16 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="D6" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="E6">
         <v>32</v>
@@ -7088,13 +7736,13 @@
         <v>1589</v>
       </c>
       <c r="G6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J6">
         <v>95.59999999999999</v>
@@ -7120,16 +7768,16 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D7" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E7">
         <v>33</v>
@@ -7138,13 +7786,13 @@
         <v>1128</v>
       </c>
       <c r="G7" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H7">
         <v>800000</v>
       </c>
       <c r="I7" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J7">
         <v>95.3</v>
@@ -7170,16 +7818,16 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="D8" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="E8">
         <v>28</v>
@@ -7188,13 +7836,13 @@
         <v>1085</v>
       </c>
       <c r="G8" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H8">
         <v>200000</v>
       </c>
       <c r="I8" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J8">
         <v>95.3</v>
@@ -7220,16 +7868,16 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D9" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="E9">
         <v>21</v>
@@ -7241,7 +7889,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J9">
         <v>95</v>
@@ -7267,16 +7915,16 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="D10" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E10">
         <v>30</v>
@@ -7285,13 +7933,13 @@
         <v>1478</v>
       </c>
       <c r="G10" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J10">
         <v>94.90000000000001</v>
@@ -7317,16 +7965,16 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D11" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="E11">
         <v>28</v>
@@ -7335,13 +7983,13 @@
         <v>2055</v>
       </c>
       <c r="G11" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J11">
         <v>94.5</v>
@@ -7367,16 +8015,16 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="D12" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="E12">
         <v>27</v>
@@ -7385,13 +8033,13 @@
         <v>1510</v>
       </c>
       <c r="G12" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="J12">
         <v>94.40000000000001</v>
@@ -7417,16 +8065,16 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D13" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="E13">
         <v>30</v>
@@ -7435,13 +8083,13 @@
         <v>1602</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J13">
         <v>94.40000000000001</v>
@@ -7467,16 +8115,16 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D14" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E14">
         <v>29</v>
@@ -7485,13 +8133,13 @@
         <v>1809</v>
       </c>
       <c r="G14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J14">
         <v>94.2</v>
@@ -7517,16 +8165,16 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="D15" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="E15">
         <v>24</v>
@@ -7535,13 +8183,13 @@
         <v>2172</v>
       </c>
       <c r="G15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J15">
         <v>94.2</v>
@@ -7567,16 +8215,16 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="D16" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E16">
         <v>24</v>
@@ -7585,13 +8233,13 @@
         <v>1726</v>
       </c>
       <c r="G16" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H16">
         <v>450000</v>
       </c>
       <c r="I16" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J16">
         <v>94.09999999999999</v>
@@ -7617,16 +8265,16 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D17" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="E17">
         <v>27</v>
@@ -7638,7 +8286,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J17">
         <v>94.09999999999999</v>
@@ -7664,16 +8312,16 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="D18" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E18">
         <v>23</v>
@@ -7682,13 +8330,13 @@
         <v>2156</v>
       </c>
       <c r="G18" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J18">
         <v>94.09999999999999</v>
@@ -7714,16 +8362,16 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="D19" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="E19">
         <v>27</v>
@@ -7732,13 +8380,13 @@
         <v>1629</v>
       </c>
       <c r="G19" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="J19">
         <v>93.90000000000001</v>
@@ -7764,16 +8412,16 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="D20" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="E20">
         <v>30</v>
@@ -7785,7 +8433,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J20">
         <v>93.8</v>
@@ -7811,16 +8459,16 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D21" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E21">
         <v>28</v>
@@ -7829,13 +8477,13 @@
         <v>1209</v>
       </c>
       <c r="G21" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H21">
         <v>3500000</v>
       </c>
       <c r="I21" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J21">
         <v>93.7</v>
@@ -7861,16 +8509,16 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D22" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="E22">
         <v>23</v>
@@ -7882,7 +8530,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J22">
         <v>93.7</v>
@@ -7908,16 +8556,16 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="D23" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="E23">
         <v>27</v>
@@ -7926,13 +8574,13 @@
         <v>1403</v>
       </c>
       <c r="G23" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H23">
         <v>500000</v>
       </c>
       <c r="I23" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="J23">
         <v>93.7</v>
@@ -7958,16 +8606,16 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="D24" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -7976,13 +8624,13 @@
         <v>1768</v>
       </c>
       <c r="G24" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H24">
         <v>700000</v>
       </c>
       <c r="I24" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J24">
         <v>93.40000000000001</v>
@@ -8008,16 +8656,16 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="D25" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="E25">
         <v>22</v>
@@ -8026,13 +8674,13 @@
         <v>1700</v>
       </c>
       <c r="G25" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J25">
         <v>93.40000000000001</v>
@@ -8058,16 +8706,16 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D26" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="E26">
         <v>31</v>
@@ -8079,7 +8727,7 @@
         <v>1500000</v>
       </c>
       <c r="I26" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J26">
         <v>93.40000000000001</v>
@@ -8142,36 +8790,36 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D2" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="E2">
         <v>30</v>
@@ -8180,13 +8828,13 @@
         <v>1528</v>
       </c>
       <c r="G2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H2">
         <v>500000</v>
       </c>
       <c r="I2" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="J2">
         <v>96.8</v>
@@ -8209,16 +8857,16 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D3" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="E3">
         <v>31</v>
@@ -8230,7 +8878,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J3">
         <v>95.09999999999999</v>
@@ -8253,16 +8901,16 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D4" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="E4">
         <v>22</v>
@@ -8271,13 +8919,13 @@
         <v>2177</v>
       </c>
       <c r="G4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J4">
         <v>94.40000000000001</v>
@@ -8300,16 +8948,16 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D5" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="E5">
         <v>30</v>
@@ -8318,13 +8966,13 @@
         <v>2099</v>
       </c>
       <c r="G5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H5">
         <v>75000</v>
       </c>
       <c r="I5" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J5">
         <v>94.3</v>
@@ -8347,16 +8995,16 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D6" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E6">
         <v>24</v>
@@ -8365,13 +9013,13 @@
         <v>1911</v>
       </c>
       <c r="G6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J6">
         <v>92.40000000000001</v>
@@ -8394,16 +9042,16 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="D7" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="E7">
         <v>30</v>
@@ -8412,13 +9060,13 @@
         <v>2131</v>
       </c>
       <c r="G7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H7">
         <v>175000</v>
       </c>
       <c r="I7" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="J7">
         <v>92.3</v>
@@ -8441,16 +9089,16 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D8" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="E8">
         <v>30</v>
@@ -8459,13 +9107,13 @@
         <v>1133</v>
       </c>
       <c r="G8" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J8">
         <v>92.09999999999999</v>
@@ -8488,16 +9136,16 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="D9" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="E9">
         <v>28</v>
@@ -8506,13 +9154,13 @@
         <v>2232</v>
       </c>
       <c r="G9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J9">
         <v>92</v>
@@ -8535,16 +9183,16 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="D10" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E10">
         <v>29</v>
@@ -8553,13 +9201,13 @@
         <v>1975</v>
       </c>
       <c r="G10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H10">
         <v>10000</v>
       </c>
       <c r="I10" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="J10">
         <v>91.59999999999999</v>
@@ -8582,16 +9230,16 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D11" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="E11">
         <v>31</v>
@@ -8603,7 +9251,7 @@
         <v>75000</v>
       </c>
       <c r="I11" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J11">
         <v>91.3</v>
@@ -8626,16 +9274,16 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="D12" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="E12">
         <v>30</v>
@@ -8644,13 +9292,13 @@
         <v>1782</v>
       </c>
       <c r="G12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="J12">
         <v>91.09999999999999</v>
@@ -8673,16 +9321,16 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="D13" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="E13">
         <v>30</v>
@@ -8691,13 +9339,13 @@
         <v>2059</v>
       </c>
       <c r="G13" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J13">
         <v>90.90000000000001</v>
@@ -8720,16 +9368,16 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D14" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="E14">
         <v>24</v>
@@ -8741,7 +9389,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J14">
         <v>90.8</v>
@@ -8764,16 +9412,16 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D15" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="E15">
         <v>33</v>
@@ -8785,7 +9433,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J15">
         <v>90.8</v>
@@ -8808,16 +9456,16 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="D16" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="E16">
         <v>29</v>
@@ -8826,13 +9474,13 @@
         <v>1625</v>
       </c>
       <c r="G16" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="H16">
         <v>2200000</v>
       </c>
       <c r="I16" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="J16">
         <v>90.7</v>
@@ -8855,16 +9503,16 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="D17" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="E17">
         <v>25</v>
@@ -8873,13 +9521,13 @@
         <v>1287</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J17">
         <v>90.5</v>
@@ -8902,16 +9550,16 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D18" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E18">
         <v>26</v>
@@ -8920,13 +9568,13 @@
         <v>2307</v>
       </c>
       <c r="G18" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J18">
         <v>89.7</v>
@@ -8949,16 +9597,16 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="D19" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="E19">
         <v>25</v>
@@ -8967,13 +9615,13 @@
         <v>1836</v>
       </c>
       <c r="G19" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H19">
         <v>250000</v>
       </c>
       <c r="I19" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J19">
         <v>89.59999999999999</v>
@@ -8996,16 +9644,16 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="D20" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="E20">
         <v>31</v>
@@ -9014,13 +9662,13 @@
         <v>1396</v>
       </c>
       <c r="G20" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H20">
         <v>500000</v>
       </c>
       <c r="I20" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="J20">
         <v>89.3</v>
@@ -9043,16 +9691,16 @@
     </row>
     <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="D21" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="E21">
         <v>29</v>
@@ -9061,13 +9709,13 @@
         <v>1343</v>
       </c>
       <c r="G21" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="J21">
         <v>88.90000000000001</v>
@@ -9090,16 +9738,16 @@
     </row>
     <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D22" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="E22">
         <v>24</v>
@@ -9111,7 +9759,7 @@
         <v>400000</v>
       </c>
       <c r="I22" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J22">
         <v>88.8</v>
@@ -9134,16 +9782,16 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="D23" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="E23">
         <v>26</v>
@@ -9152,13 +9800,13 @@
         <v>1124</v>
       </c>
       <c r="G23" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J23">
         <v>88.7</v>
@@ -9181,16 +9829,16 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="D24" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="E24">
         <v>32</v>
@@ -9199,13 +9847,13 @@
         <v>1595</v>
       </c>
       <c r="G24" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H24">
         <v>375000</v>
       </c>
       <c r="I24" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J24">
         <v>88.7</v>
@@ -9228,16 +9876,16 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="D25" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="E25">
         <v>27</v>
@@ -9246,13 +9894,13 @@
         <v>2016</v>
       </c>
       <c r="G25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H25">
         <v>350000</v>
       </c>
       <c r="I25" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J25">
         <v>88.3</v>
@@ -9275,16 +9923,16 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="D26" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -9296,7 +9944,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="J26">
         <v>88.09999999999999</v>
@@ -9379,16 +10027,16 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="D2" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="E2">
         <v>32</v>
@@ -9397,13 +10045,13 @@
         <v>1382</v>
       </c>
       <c r="G2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H2">
         <v>2000000</v>
       </c>
       <c r="I2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J2">
         <v>95.2</v>
@@ -9429,16 +10077,16 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="D3" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="E3">
         <v>25</v>
@@ -9447,13 +10095,13 @@
         <v>1326</v>
       </c>
       <c r="G3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J3">
         <v>95.09999999999999</v>
@@ -9479,16 +10127,16 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="D4" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="E4">
         <v>29</v>
@@ -9497,13 +10145,13 @@
         <v>3548</v>
       </c>
       <c r="G4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="J4">
         <v>94.8</v>
@@ -9529,16 +10177,16 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="D5" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="E5">
         <v>26</v>
@@ -9547,13 +10195,13 @@
         <v>2383</v>
       </c>
       <c r="G5" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="H5">
         <v>5000000</v>
       </c>
       <c r="I5" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="J5">
         <v>94.40000000000001</v>
@@ -9579,16 +10227,16 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="D6" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="E6">
         <v>30</v>
@@ -9600,7 +10248,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J6">
         <v>93.90000000000001</v>
@@ -9626,16 +10274,16 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="D7" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E7">
         <v>29</v>
@@ -9644,13 +10292,13 @@
         <v>3557</v>
       </c>
       <c r="G7" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H7">
         <v>1800000</v>
       </c>
       <c r="I7" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="J7">
         <v>93.8</v>
@@ -9676,16 +10324,16 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="D8" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="E8">
         <v>25</v>
@@ -9694,13 +10342,13 @@
         <v>1413</v>
       </c>
       <c r="G8" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="H8">
         <v>1000000</v>
       </c>
       <c r="I8" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J8">
         <v>93.59999999999999</v>
@@ -9726,16 +10374,16 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D9" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="E9">
         <v>23</v>
@@ -9744,13 +10392,13 @@
         <v>2899</v>
       </c>
       <c r="G9" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J9">
         <v>93.5</v>
@@ -9776,16 +10424,16 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="D10" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="E10">
         <v>28</v>
@@ -9794,13 +10442,13 @@
         <v>1683</v>
       </c>
       <c r="G10" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J10">
         <v>92.90000000000001</v>
@@ -9826,16 +10474,16 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="D11" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="E11">
         <v>30</v>
@@ -9844,13 +10492,13 @@
         <v>2529</v>
       </c>
       <c r="G11" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="H11">
         <v>600000</v>
       </c>
       <c r="I11" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="J11">
         <v>92.59999999999999</v>
@@ -9876,16 +10524,16 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="D12" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="E12">
         <v>32</v>
@@ -9897,7 +10545,7 @@
         <v>500000</v>
       </c>
       <c r="I12" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J12">
         <v>92.59999999999999</v>
@@ -9923,16 +10571,16 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="D13" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="E13">
         <v>31</v>
@@ -9941,13 +10589,13 @@
         <v>2019</v>
       </c>
       <c r="G13" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H13">
         <v>800000</v>
       </c>
       <c r="I13" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J13">
         <v>92.5</v>
@@ -9973,16 +10621,16 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="D14" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="E14">
         <v>31</v>
@@ -9991,13 +10639,13 @@
         <v>1483</v>
       </c>
       <c r="G14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H14">
         <v>350000</v>
       </c>
       <c r="I14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J14">
         <v>92.5</v>
@@ -10023,16 +10671,16 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="D15" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="E15">
         <v>29</v>
@@ -10041,13 +10689,13 @@
         <v>1201</v>
       </c>
       <c r="G15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H15">
         <v>4500000</v>
       </c>
       <c r="I15" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J15">
         <v>92.40000000000001</v>
@@ -10073,16 +10721,16 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="D16" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="E16">
         <v>28</v>
@@ -10091,13 +10739,13 @@
         <v>2745</v>
       </c>
       <c r="G16" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H16">
         <v>15000000</v>
       </c>
       <c r="I16" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="J16">
         <v>92.09999999999999</v>
@@ -10123,16 +10771,16 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D17" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="E17">
         <v>27</v>
@@ -10141,13 +10789,13 @@
         <v>1295</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J17">
         <v>92</v>
@@ -10173,16 +10821,16 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="D18" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="E18">
         <v>27</v>
@@ -10191,13 +10839,13 @@
         <v>2691</v>
       </c>
       <c r="G18" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J18">
         <v>91.8</v>
@@ -10223,16 +10871,16 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="D19" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="E19">
         <v>22</v>
@@ -10241,13 +10889,13 @@
         <v>1202</v>
       </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J19">
         <v>91.7</v>
@@ -10273,16 +10921,16 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="D20" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="E20">
         <v>30</v>
@@ -10294,7 +10942,7 @@
         <v>175000</v>
       </c>
       <c r="I20" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J20">
         <v>91.7</v>
@@ -10320,16 +10968,16 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="D21" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="E21">
         <v>33</v>
@@ -10338,13 +10986,13 @@
         <v>1367</v>
       </c>
       <c r="G21" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H21">
         <v>1400000</v>
       </c>
       <c r="I21" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J21">
         <v>91.5</v>
@@ -10370,16 +11018,16 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="D22" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="E22">
         <v>25</v>
@@ -10391,7 +11039,7 @@
         <v>500000</v>
       </c>
       <c r="I22" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="J22">
         <v>91.2</v>
@@ -10417,16 +11065,16 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="D23" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E23">
         <v>27</v>
@@ -10435,13 +11083,13 @@
         <v>3542</v>
       </c>
       <c r="G23" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J23">
         <v>91.09999999999999</v>
@@ -10467,16 +11115,16 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="D24" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -10485,13 +11133,13 @@
         <v>1854</v>
       </c>
       <c r="G24" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J24">
         <v>91</v>
@@ -10517,16 +11165,16 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D25" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="E25">
         <v>32</v>
@@ -10535,13 +11183,13 @@
         <v>2595</v>
       </c>
       <c r="G25" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="H25">
         <v>300000</v>
       </c>
       <c r="I25" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="J25">
         <v>90.90000000000001</v>
@@ -10567,16 +11215,16 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="D26" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="E26">
         <v>22</v>
@@ -10585,13 +11233,13 @@
         <v>2098</v>
       </c>
       <c r="G26" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J26">
         <v>90.40000000000001</v>
@@ -10654,36 +11302,36 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="D2" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="E2">
         <v>22</v>
@@ -10692,13 +11340,13 @@
         <v>1190</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H2">
         <v>2500000</v>
       </c>
       <c r="I2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J2">
         <v>94.59999999999999</v>
@@ -10721,16 +11369,16 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="D3" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="E3">
         <v>30</v>
@@ -10739,13 +11387,13 @@
         <v>1864</v>
       </c>
       <c r="G3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H3">
         <v>5000000</v>
       </c>
       <c r="I3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J3">
         <v>94.59999999999999</v>
@@ -10768,16 +11416,16 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="D4" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="E4">
         <v>29</v>
@@ -10786,13 +11434,13 @@
         <v>1437</v>
       </c>
       <c r="G4" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H4">
         <v>400000</v>
       </c>
       <c r="I4" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="J4">
         <v>94.40000000000001</v>
@@ -10815,16 +11463,16 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="D5" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="E5">
         <v>32</v>
@@ -10833,13 +11481,13 @@
         <v>2371</v>
       </c>
       <c r="G5" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H5">
         <v>300000</v>
       </c>
       <c r="I5" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J5">
         <v>94.09999999999999</v>
@@ -10862,16 +11510,16 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="D6" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="E6">
         <v>29</v>
@@ -10880,13 +11528,13 @@
         <v>2034</v>
       </c>
       <c r="G6" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J6">
         <v>93.7</v>
@@ -10909,16 +11557,16 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="D7" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="E7">
         <v>31</v>
@@ -10927,13 +11575,13 @@
         <v>1834</v>
       </c>
       <c r="G7" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H7">
         <v>800000</v>
       </c>
       <c r="I7" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="J7">
         <v>92.09999999999999</v>
@@ -10956,16 +11604,16 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="D8" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="E8">
         <v>27</v>
@@ -10974,13 +11622,13 @@
         <v>3268</v>
       </c>
       <c r="G8" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H8">
         <v>250000</v>
       </c>
       <c r="I8" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J8">
         <v>91.90000000000001</v>
@@ -11003,16 +11651,16 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="D9" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="E9">
         <v>30</v>
@@ -11021,13 +11669,13 @@
         <v>1947</v>
       </c>
       <c r="G9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H9">
         <v>1000000</v>
       </c>
       <c r="I9" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="J9">
         <v>91.7</v>
@@ -11050,16 +11698,16 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="D10" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="E10">
         <v>30</v>
@@ -11068,13 +11716,13 @@
         <v>1448</v>
       </c>
       <c r="G10" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H10">
         <v>3000000</v>
       </c>
       <c r="I10" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J10">
         <v>91.2</v>
@@ -11097,16 +11745,16 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="D11" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="E11">
         <v>30</v>
@@ -11118,7 +11766,7 @@
         <v>200000</v>
       </c>
       <c r="I11" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J11">
         <v>91.09999999999999</v>
@@ -11141,16 +11789,16 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="D12" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="E12">
         <v>24</v>
@@ -11159,13 +11807,13 @@
         <v>1172</v>
       </c>
       <c r="G12" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H12">
         <v>100000</v>
       </c>
       <c r="I12" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J12">
         <v>90.8</v>
@@ -11188,16 +11836,16 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="D13" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="E13">
         <v>27</v>
@@ -11206,13 +11854,13 @@
         <v>2833</v>
       </c>
       <c r="G13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J13">
         <v>90.7</v>
@@ -11235,16 +11883,16 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="D14" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="E14">
         <v>32</v>
@@ -11256,7 +11904,7 @@
         <v>200000</v>
       </c>
       <c r="I14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J14">
         <v>90.2</v>
@@ -11279,16 +11927,16 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="D15" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="E15">
         <v>24</v>
@@ -11300,7 +11948,7 @@
         <v>3000000</v>
       </c>
       <c r="I15" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="J15">
         <v>90.09999999999999</v>
@@ -11323,16 +11971,16 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="D16" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="E16">
         <v>31</v>
@@ -11341,13 +11989,13 @@
         <v>2745</v>
       </c>
       <c r="G16" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J16">
         <v>89.40000000000001</v>
@@ -11370,16 +12018,16 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="D17" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="E17">
         <v>30</v>
@@ -11388,13 +12036,13 @@
         <v>2643</v>
       </c>
       <c r="G17" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="H17">
         <v>300000</v>
       </c>
       <c r="I17" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="J17">
         <v>88.5</v>
@@ -11417,16 +12065,16 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="D18" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="E18">
         <v>28</v>
@@ -11435,13 +12083,13 @@
         <v>3835</v>
       </c>
       <c r="G18" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H18">
         <v>800000</v>
       </c>
       <c r="I18" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J18">
         <v>88.3</v>
@@ -11464,16 +12112,16 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="D19" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="E19">
         <v>32</v>
@@ -11485,7 +12133,7 @@
         <v>175000</v>
       </c>
       <c r="I19" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J19">
         <v>88.2</v>
@@ -11508,16 +12156,16 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="D20" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="E20">
         <v>32</v>
@@ -11529,7 +12177,7 @@
         <v>850000</v>
       </c>
       <c r="I20" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J20">
         <v>87.8</v>
@@ -11552,16 +12200,16 @@
     </row>
     <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="D21" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="E21">
         <v>26</v>
@@ -11570,13 +12218,13 @@
         <v>1324</v>
       </c>
       <c r="G21" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H21">
         <v>850000</v>
       </c>
       <c r="I21" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J21">
         <v>87.40000000000001</v>
@@ -11599,16 +12247,16 @@
     </row>
     <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C22" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="D22" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E22">
         <v>26</v>
@@ -11617,13 +12265,13 @@
         <v>1775</v>
       </c>
       <c r="G22" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H22">
         <v>250000</v>
       </c>
       <c r="I22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J22">
         <v>87.2</v>
@@ -11646,16 +12294,16 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="D23" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="E23">
         <v>31</v>
@@ -11664,13 +12312,13 @@
         <v>2806</v>
       </c>
       <c r="G23" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="H23">
         <v>1000000</v>
       </c>
       <c r="I23" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="J23">
         <v>86.8</v>
@@ -11693,16 +12341,16 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="D24" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="E24">
         <v>25</v>
@@ -11711,13 +12359,13 @@
         <v>1732</v>
       </c>
       <c r="G24" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J24">
         <v>86.59999999999999</v>
@@ -11740,16 +12388,16 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="D25" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="E25">
         <v>32</v>
@@ -11758,13 +12406,13 @@
         <v>1395</v>
       </c>
       <c r="G25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H25">
         <v>450000</v>
       </c>
       <c r="I25" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J25">
         <v>86.40000000000001</v>
@@ -11787,16 +12435,16 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="D26" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -11805,13 +12453,13 @@
         <v>3522</v>
       </c>
       <c r="G26" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H26">
         <v>3300000</v>
       </c>
       <c r="I26" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J26">
         <v>85.59999999999999</v>

--- a/Santa Cruz V2/listas/bola_parada_especialistas.xlsx
+++ b/Santa Cruz V2/listas/bola_parada_especialistas.xlsx
@@ -1070,12 +1070,12 @@
     <t>Evander</t>
   </si>
   <si>
+    <t>J. Bartolo</t>
+  </si>
+  <si>
     <t>Arthur Rezende</t>
   </si>
   <si>
-    <t>J. Bartolo</t>
-  </si>
-  <si>
     <t>Valdívia</t>
   </si>
   <si>
@@ -1088,12 +1088,12 @@
     <t>Everton Bala</t>
   </si>
   <si>
+    <t>Thauan Lara</t>
+  </si>
+  <si>
     <t>Gabriel Honório</t>
   </si>
   <si>
-    <t>Thauan Lara</t>
-  </si>
-  <si>
     <t>Gustavo Sauer</t>
   </si>
   <si>
@@ -1145,12 +1145,12 @@
     <t>Cincinnati</t>
   </si>
   <si>
+    <t>Asteras Tripolis</t>
+  </si>
+  <si>
     <t>Muharraq</t>
   </si>
   <si>
-    <t>Asteras Tripolis</t>
-  </si>
-  <si>
     <t>Jeonnam Dragons</t>
   </si>
   <si>
@@ -1280,10 +1280,10 @@
     <t>Wesley</t>
   </si>
   <si>
+    <t>Iago Maidana</t>
+  </si>
+  <si>
     <t>Gastón Valles</t>
-  </si>
-  <si>
-    <t>Iago Maidana</t>
   </si>
   <si>
     <t>Mateus Sarará</t>
@@ -10424,10 +10424,10 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
         <v>349</v>
@@ -10436,45 +10436,48 @@
         <v>374</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F10">
-        <v>1839</v>
+        <v>2529</v>
+      </c>
+      <c r="G10" t="s">
+        <v>389</v>
       </c>
       <c r="H10">
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="I10" t="s">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="J10">
         <v>92.59999999999999</v>
       </c>
       <c r="K10">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="L10">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="M10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N10">
-        <v>22.2</v>
+        <v>37.5</v>
       </c>
       <c r="O10">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="P10">
-        <v>38.1</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
         <v>350</v>
@@ -10483,40 +10486,37 @@
         <v>375</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>2529</v>
-      </c>
-      <c r="G11" t="s">
-        <v>389</v>
+        <v>1839</v>
       </c>
       <c r="H11">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="I11" t="s">
-        <v>180</v>
+        <v>82</v>
       </c>
       <c r="J11">
         <v>92.59999999999999</v>
       </c>
       <c r="K11">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="L11">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="M11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N11">
-        <v>37.5</v>
+        <v>22.2</v>
       </c>
       <c r="O11">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="P11">
-        <v>28.6</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -10721,7 +10721,7 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
@@ -10730,16 +10730,19 @@
         <v>355</v>
       </c>
       <c r="D16" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="E16">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F16">
-        <v>1443</v>
+        <v>1202</v>
+      </c>
+      <c r="G16" t="s">
+        <v>76</v>
       </c>
       <c r="H16">
-        <v>175000</v>
+        <v>0</v>
       </c>
       <c r="I16" t="s">
         <v>82</v>
@@ -10748,27 +10751,27 @@
         <v>91.7</v>
       </c>
       <c r="K16">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="L16">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="M16">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N16">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="O16">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="P16">
-        <v>34.9</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B17" t="s">
         <v>23</v>
@@ -10777,19 +10780,16 @@
         <v>356</v>
       </c>
       <c r="D17" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="E17">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F17">
-        <v>1202</v>
-      </c>
-      <c r="G17" t="s">
-        <v>76</v>
+        <v>1443</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>175000</v>
       </c>
       <c r="I17" t="s">
         <v>82</v>
@@ -10798,22 +10798,22 @@
         <v>91.7</v>
       </c>
       <c r="K17">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="L17">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="M17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="O17">
-        <v>0.29</v>
+        <v>0.17</v>
       </c>
       <c r="P17">
-        <v>21.7</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -12341,96 +12341,96 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>396</v>
+        <v>337</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s">
         <v>419</v>
       </c>
       <c r="D24" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="E24">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F24">
-        <v>1572</v>
+        <v>1533</v>
       </c>
       <c r="G24" t="s">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="I24" t="s">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="J24">
         <v>85.09999999999999</v>
       </c>
       <c r="K24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="M24">
-        <v>7.27</v>
+        <v>4.99</v>
       </c>
       <c r="N24">
-        <v>39.4</v>
+        <v>58.8</v>
       </c>
       <c r="O24">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>337</v>
+        <v>396</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
         <v>420</v>
       </c>
       <c r="D25" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="E25">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F25">
-        <v>1533</v>
+        <v>1572</v>
       </c>
       <c r="G25" t="s">
-        <v>73</v>
+        <v>178</v>
       </c>
       <c r="H25">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="J25">
         <v>85.09999999999999</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="M25">
-        <v>4.99</v>
+        <v>7.27</v>
       </c>
       <c r="N25">
-        <v>58.8</v>
+        <v>39.4</v>
       </c>
       <c r="O25">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" spans="1:15">

--- a/Santa Cruz V2/listas/bola_parada_especialistas.xlsx
+++ b/Santa Cruz V2/listas/bola_parada_especialistas.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="442">
   <si>
     <t>liga</t>
   </si>
@@ -104,12 +104,12 @@
     <t>EE</t>
   </si>
   <si>
+    <t>LD</t>
+  </si>
+  <si>
     <t>MEI</t>
   </si>
   <si>
-    <t>LD</t>
-  </si>
-  <si>
     <t>CA</t>
   </si>
   <si>
@@ -128,9 +128,6 @@
     <t>Iago Teles</t>
   </si>
   <si>
-    <t>Dodô</t>
-  </si>
-  <si>
     <t>Pepê</t>
   </si>
   <si>
@@ -173,12 +170,12 @@
     <t>Gegé</t>
   </si>
   <si>
+    <t>Mikael Doka</t>
+  </si>
+  <si>
     <t>Jean Lucas</t>
   </si>
   <si>
-    <t>Mikael Doka</t>
-  </si>
-  <si>
     <t>Dadá Belmonte</t>
   </si>
   <si>
@@ -191,6 +188,9 @@
     <t>Pará</t>
   </si>
   <si>
+    <t>Wesley Pinheiro</t>
+  </si>
+  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -203,205 +203,205 @@
     <t>Londrina</t>
   </si>
   <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
+    <t>América-MG</t>
+  </si>
+  <si>
+    <t>Athletic</t>
+  </si>
+  <si>
+    <t>Sport</t>
+  </si>
+  <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
+    <t>Operário-PR</t>
+  </si>
+  <si>
+    <t>Avaí</t>
+  </si>
+  <si>
+    <t>Ceará</t>
+  </si>
+  <si>
+    <t>Juventude</t>
+  </si>
+  <si>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>Goiás</t>
+  </si>
+  <si>
+    <t>Atlético-GO</t>
+  </si>
+  <si>
+    <t>2026-12-31</t>
+  </si>
+  <si>
+    <t>2026-11-30</t>
+  </si>
+  <si>
+    <t>2027-12-31</t>
+  </si>
+  <si>
+    <t>2027-06-30</t>
+  </si>
+  <si>
+    <t>2029-07-31</t>
+  </si>
+  <si>
+    <t>2027-11-30</t>
+  </si>
+  <si>
+    <t>2028-12-31</t>
+  </si>
+  <si>
+    <t>2027-03-31</t>
+  </si>
+  <si>
+    <t>Venezuela</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Brazil, Italy</t>
+  </si>
+  <si>
+    <t>Brazil, Germany</t>
+  </si>
+  <si>
+    <t>indice_finalizador</t>
+  </si>
+  <si>
+    <t>Head goals</t>
+  </si>
+  <si>
+    <t>Head goals per 90</t>
+  </si>
+  <si>
+    <t>Aerial duels per 90</t>
+  </si>
+  <si>
+    <t>Aerial duels won, %</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>finalizador_2025</t>
+  </si>
+  <si>
+    <t>gols_cabeca_2025</t>
+  </si>
+  <si>
+    <t>gols_bp_2026</t>
+  </si>
+  <si>
+    <t>gols_bp_3t</t>
+  </si>
+  <si>
+    <t>gols_bp_cabeca_3t</t>
+  </si>
+  <si>
+    <t>xg_bp_3t</t>
+  </si>
+  <si>
+    <t>ZE</t>
+  </si>
+  <si>
+    <t>ZD</t>
+  </si>
+  <si>
+    <t>Luiz Otávio</t>
+  </si>
+  <si>
+    <t>Vilar</t>
+  </si>
+  <si>
+    <t>Alisson Safira</t>
+  </si>
+  <si>
+    <t>Matheus Bianqui</t>
+  </si>
+  <si>
+    <t>Yago Lincoln</t>
+  </si>
+  <si>
+    <t>Dudu</t>
+  </si>
+  <si>
+    <t>Messias</t>
+  </si>
+  <si>
+    <t>Gabriel Pinheiro</t>
+  </si>
+  <si>
+    <t>Kadu</t>
+  </si>
+  <si>
+    <t>Mikael</t>
+  </si>
+  <si>
+    <t>Paulo Vitor</t>
+  </si>
+  <si>
+    <t>Everton Morelli</t>
+  </si>
+  <si>
+    <t>Léo Índio</t>
+  </si>
+  <si>
+    <t>Benevenuto</t>
+  </si>
+  <si>
+    <t>Júlio César</t>
+  </si>
+  <si>
+    <t>J. Miritello</t>
+  </si>
+  <si>
+    <t>André Luiz</t>
+  </si>
+  <si>
+    <t>Léo Gomes</t>
+  </si>
+  <si>
+    <t>Perotti</t>
+  </si>
+  <si>
+    <t>Bruno José</t>
+  </si>
+  <si>
+    <t>Gustavo Coutinho</t>
+  </si>
+  <si>
+    <t>G. Mastriani</t>
+  </si>
+  <si>
+    <t>Kauan Cristtyan</t>
+  </si>
+  <si>
+    <t>Willean Lepo</t>
+  </si>
+  <si>
+    <t>Novorizontino</t>
+  </si>
+  <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
     <t>Náutico</t>
-  </si>
-  <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
-    <t>América-MG</t>
-  </si>
-  <si>
-    <t>Athletic</t>
-  </si>
-  <si>
-    <t>Sport</t>
-  </si>
-  <si>
-    <t>Fortaleza</t>
-  </si>
-  <si>
-    <t>Operário-PR</t>
-  </si>
-  <si>
-    <t>Avaí</t>
-  </si>
-  <si>
-    <t>Ceará</t>
-  </si>
-  <si>
-    <t>Juventude</t>
-  </si>
-  <si>
-    <t>CRB</t>
-  </si>
-  <si>
-    <t>Goiás</t>
-  </si>
-  <si>
-    <t>Atlético-GO</t>
-  </si>
-  <si>
-    <t>2026-12-31</t>
-  </si>
-  <si>
-    <t>2026-11-30</t>
-  </si>
-  <si>
-    <t>2027-12-31</t>
-  </si>
-  <si>
-    <t>2027-06-30</t>
-  </si>
-  <si>
-    <t>2029-07-31</t>
-  </si>
-  <si>
-    <t>2027-11-30</t>
-  </si>
-  <si>
-    <t>2028-12-31</t>
-  </si>
-  <si>
-    <t>2027-03-31</t>
-  </si>
-  <si>
-    <t>Venezuela</t>
-  </si>
-  <si>
-    <t>Brazil</t>
-  </si>
-  <si>
-    <t>Paraguay</t>
-  </si>
-  <si>
-    <t>Ecuador</t>
-  </si>
-  <si>
-    <t>Brazil, Italy</t>
-  </si>
-  <si>
-    <t>Brazil, Germany</t>
-  </si>
-  <si>
-    <t>indice_finalizador</t>
-  </si>
-  <si>
-    <t>Head goals</t>
-  </si>
-  <si>
-    <t>Head goals per 90</t>
-  </si>
-  <si>
-    <t>Aerial duels per 90</t>
-  </si>
-  <si>
-    <t>Aerial duels won, %</t>
-  </si>
-  <si>
-    <t>Height</t>
-  </si>
-  <si>
-    <t>finalizador_2025</t>
-  </si>
-  <si>
-    <t>gols_cabeca_2025</t>
-  </si>
-  <si>
-    <t>gols_bp_2026</t>
-  </si>
-  <si>
-    <t>gols_bp_3t</t>
-  </si>
-  <si>
-    <t>gols_bp_cabeca_3t</t>
-  </si>
-  <si>
-    <t>xg_bp_3t</t>
-  </si>
-  <si>
-    <t>ZE</t>
-  </si>
-  <si>
-    <t>ZD</t>
-  </si>
-  <si>
-    <t>Luiz Otávio</t>
-  </si>
-  <si>
-    <t>Vilar</t>
-  </si>
-  <si>
-    <t>Alisson Safira</t>
-  </si>
-  <si>
-    <t>Matheus Bianqui</t>
-  </si>
-  <si>
-    <t>Yago Lincoln</t>
-  </si>
-  <si>
-    <t>Dudu</t>
-  </si>
-  <si>
-    <t>Messias</t>
-  </si>
-  <si>
-    <t>Gabriel Pinheiro</t>
-  </si>
-  <si>
-    <t>Kadu</t>
-  </si>
-  <si>
-    <t>Mikael</t>
-  </si>
-  <si>
-    <t>Paulo Vitor</t>
-  </si>
-  <si>
-    <t>Everton Morelli</t>
-  </si>
-  <si>
-    <t>Léo Índio</t>
-  </si>
-  <si>
-    <t>Benevenuto</t>
-  </si>
-  <si>
-    <t>Júlio César</t>
-  </si>
-  <si>
-    <t>J. Miritello</t>
-  </si>
-  <si>
-    <t>André Luiz</t>
-  </si>
-  <si>
-    <t>Léo Gomes</t>
-  </si>
-  <si>
-    <t>Perotti</t>
-  </si>
-  <si>
-    <t>Bruno José</t>
-  </si>
-  <si>
-    <t>Gustavo Coutinho</t>
-  </si>
-  <si>
-    <t>G. Mastriani</t>
-  </si>
-  <si>
-    <t>Kauan Cristtyan</t>
-  </si>
-  <si>
-    <t>Willean Lepo</t>
-  </si>
-  <si>
-    <t>Novorizontino</t>
-  </si>
-  <si>
-    <t>Vila Nova</t>
   </si>
   <si>
     <t>Ponte Preta</t>
@@ -1795,13 +1795,13 @@
         <v>1477</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H2">
         <v>800000</v>
       </c>
       <c r="I2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J2">
         <v>96.5</v>
@@ -1857,13 +1857,13 @@
         <v>1987</v>
       </c>
       <c r="G3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H3">
         <v>600000</v>
       </c>
       <c r="I3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J3">
         <v>95.90000000000001</v>
@@ -1925,10 +1925,10 @@
         <v>2106</v>
       </c>
       <c r="G4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J4">
         <v>95.2</v>
@@ -1984,10 +1984,10 @@
         <v>1103</v>
       </c>
       <c r="G5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J5">
         <v>92</v>
@@ -2028,7 +2028,7 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
@@ -2037,55 +2037,49 @@
         <v>60</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>1516</v>
+        <v>1571</v>
       </c>
       <c r="G6" t="s">
         <v>74</v>
       </c>
       <c r="I6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J6">
-        <v>91.7</v>
+        <v>91.2</v>
       </c>
       <c r="K6">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="L6">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N6">
-        <v>44.4</v>
+        <v>33.3</v>
       </c>
       <c r="O6">
-        <v>0.34</v>
+        <v>0.13</v>
       </c>
       <c r="P6">
-        <v>22.6</v>
-      </c>
-      <c r="Q6">
-        <v>95.2</v>
-      </c>
-      <c r="R6">
-        <v>76</v>
+        <v>35.7</v>
       </c>
       <c r="S6">
+        <v>3</v>
+      </c>
+      <c r="T6">
+        <v>3</v>
+      </c>
+      <c r="U6">
         <v>2</v>
       </c>
-      <c r="T6">
-        <v>5</v>
-      </c>
-      <c r="U6">
-        <v>4</v>
-      </c>
       <c r="V6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -2093,7 +2087,7 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
         <v>36</v>
@@ -2102,43 +2096,43 @@
         <v>61</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>1571</v>
+        <v>1303</v>
       </c>
       <c r="G7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I7" t="s">
         <v>82</v>
       </c>
       <c r="J7">
-        <v>91.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="K7">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="L7">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="M7">
         <v>3</v>
       </c>
       <c r="N7">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="O7">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="P7">
-        <v>35.7</v>
+        <v>38.7</v>
       </c>
       <c r="S7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U7">
         <v>2</v>
@@ -2152,7 +2146,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
@@ -2164,43 +2158,43 @@
         <v>23</v>
       </c>
       <c r="F8">
-        <v>1303</v>
+        <v>1011</v>
       </c>
       <c r="G8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I8" t="s">
         <v>83</v>
       </c>
       <c r="J8">
-        <v>90.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="K8">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="L8">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M8">
         <v>3</v>
       </c>
       <c r="N8">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="O8">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="P8">
-        <v>38.7</v>
+        <v>33.3</v>
       </c>
       <c r="S8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V8">
         <v>0</v>
@@ -2211,7 +2205,7 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
         <v>38</v>
@@ -2220,43 +2214,43 @@
         <v>63</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>1011</v>
+        <v>1991</v>
       </c>
       <c r="G9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J9">
-        <v>90.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="K9">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="L9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M9">
         <v>3</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="O9">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="P9">
-        <v>33.3</v>
+        <v>41.8</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U9">
         <v>0</v>
@@ -2270,7 +2264,7 @@
         <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
         <v>39</v>
@@ -2279,49 +2273,55 @@
         <v>64</v>
       </c>
       <c r="E10">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F10">
-        <v>1991</v>
+        <v>1838</v>
       </c>
       <c r="G10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J10">
-        <v>90.09999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="K10">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="L10">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="M10">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N10">
-        <v>33.3</v>
+        <v>12.5</v>
       </c>
       <c r="O10">
         <v>0.22</v>
       </c>
       <c r="P10">
-        <v>41.8</v>
+        <v>23</v>
+      </c>
+      <c r="Q10">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="R10">
+        <v>67</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
         <v>2</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -2338,55 +2338,55 @@
         <v>65</v>
       </c>
       <c r="E11">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>1838</v>
+        <v>2396</v>
       </c>
       <c r="G11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J11">
-        <v>89.5</v>
+        <v>89</v>
       </c>
       <c r="K11">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="L11">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="M11">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="N11">
-        <v>12.5</v>
+        <v>47.1</v>
       </c>
       <c r="O11">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="P11">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Q11">
-        <v>90.59999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="R11">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="S11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U11">
         <v>1</v>
       </c>
       <c r="V11">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -2394,7 +2394,7 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
         <v>41</v>
@@ -2403,55 +2403,52 @@
         <v>66</v>
       </c>
       <c r="E12">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F12">
-        <v>2396</v>
+        <v>1313</v>
       </c>
       <c r="G12" t="s">
-        <v>78</v>
+        <v>72</v>
+      </c>
+      <c r="H12">
+        <v>750000</v>
       </c>
       <c r="I12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="J12">
-        <v>89</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="K12">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="L12">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="M12">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="N12">
-        <v>47.1</v>
+        <v>20</v>
       </c>
       <c r="O12">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="P12">
-        <v>20</v>
-      </c>
-      <c r="Q12">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="R12">
-        <v>102</v>
+        <v>44.4</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
       <c r="T12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -2459,7 +2456,7 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
         <v>42</v>
@@ -2468,49 +2465,46 @@
         <v>67</v>
       </c>
       <c r="E13">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>1313</v>
+        <v>1761</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
-      </c>
-      <c r="H13">
-        <v>750000</v>
+        <v>78</v>
       </c>
       <c r="I13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J13">
-        <v>88.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="K13">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="L13">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="O13">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="P13">
-        <v>44.4</v>
+        <v>30.2</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -2521,52 +2515,61 @@
         <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
         <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F14">
-        <v>1761</v>
+        <v>1569</v>
       </c>
       <c r="G14" t="s">
-        <v>79</v>
+        <v>72</v>
+      </c>
+      <c r="H14">
+        <v>500000</v>
       </c>
       <c r="I14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J14">
-        <v>88</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K14">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N14">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="O14">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="P14">
-        <v>30.2</v>
+        <v>46.4</v>
+      </c>
+      <c r="Q14">
+        <v>79.2</v>
+      </c>
+      <c r="R14">
+        <v>18</v>
       </c>
       <c r="S14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U14">
         <v>3</v>
@@ -2580,64 +2583,61 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
         <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E15">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F15">
-        <v>1569</v>
+        <v>2186</v>
       </c>
       <c r="G15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H15">
-        <v>500000</v>
+        <v>72</v>
       </c>
       <c r="I15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J15">
-        <v>87.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="K15">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L15">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="M15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N15">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="O15">
         <v>0.11</v>
       </c>
       <c r="P15">
-        <v>46.4</v>
+        <v>32.3</v>
       </c>
       <c r="Q15">
-        <v>79.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R15">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -2648,64 +2648,67 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
         <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E16">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F16">
-        <v>2186</v>
+        <v>2301</v>
       </c>
       <c r="G16" t="s">
         <v>73</v>
       </c>
+      <c r="H16">
+        <v>125000</v>
+      </c>
       <c r="I16" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J16">
-        <v>86.7</v>
+        <v>84.5</v>
       </c>
       <c r="K16">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L16">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="M16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N16">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="O16">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="P16">
-        <v>32.3</v>
+        <v>32</v>
       </c>
       <c r="Q16">
-        <v>92.90000000000001</v>
+        <v>61</v>
       </c>
       <c r="R16">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U16">
         <v>2</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2719,61 +2722,55 @@
         <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E17">
         <v>29</v>
       </c>
       <c r="F17">
-        <v>2301</v>
+        <v>1941</v>
       </c>
       <c r="G17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H17">
-        <v>125000</v>
+        <v>900000</v>
       </c>
       <c r="I17" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="J17">
-        <v>84.5</v>
+        <v>84.2</v>
       </c>
       <c r="K17">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>17</v>
       </c>
       <c r="M17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N17">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="O17">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="P17">
-        <v>32</v>
-      </c>
-      <c r="Q17">
-        <v>61</v>
-      </c>
-      <c r="R17">
-        <v>6</v>
+        <v>48.3</v>
       </c>
       <c r="S17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -2781,7 +2778,7 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
         <v>47</v>
@@ -2793,49 +2790,49 @@
         <v>29</v>
       </c>
       <c r="F18">
-        <v>1941</v>
+        <v>1435</v>
       </c>
       <c r="G18" t="s">
         <v>73</v>
       </c>
       <c r="H18">
-        <v>900000</v>
+        <v>1000000</v>
       </c>
       <c r="I18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J18">
         <v>84.2</v>
       </c>
       <c r="K18">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L18">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M18">
+        <v>9</v>
+      </c>
+      <c r="N18">
+        <v>11.1</v>
+      </c>
+      <c r="O18">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P18">
+        <v>36.4</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
         <v>3</v>
       </c>
-      <c r="N18">
-        <v>66.7</v>
-      </c>
-      <c r="O18">
-        <v>0.08</v>
-      </c>
-      <c r="P18">
-        <v>48.3</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
       <c r="U18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -2843,61 +2840,67 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
         <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E19">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F19">
-        <v>1435</v>
+        <v>1015</v>
       </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H19">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="I19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J19">
-        <v>84.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K19">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L19">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M19">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N19">
-        <v>11.1</v>
+        <v>50</v>
       </c>
       <c r="O19">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="P19">
-        <v>36.4</v>
+        <v>21</v>
+      </c>
+      <c r="Q19">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="R19">
+        <v>97</v>
       </c>
       <c r="S19">
         <v>0</v>
       </c>
       <c r="T19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V19">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -2905,67 +2908,61 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
         <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E20">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F20">
-        <v>1015</v>
+        <v>1877</v>
       </c>
       <c r="G20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H20">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="I20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J20">
-        <v>83.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K20">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="L20">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N20">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="P20">
-        <v>21</v>
-      </c>
-      <c r="Q20">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="R20">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
       <c r="T20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -2973,13 +2970,13 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
         <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E21">
         <v>31</v>
@@ -2988,13 +2985,13 @@
         <v>1972</v>
       </c>
       <c r="G21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H21">
         <v>250000</v>
       </c>
       <c r="I21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J21">
         <v>83.09999999999999</v>
@@ -3035,58 +3032,61 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
         <v>51</v>
       </c>
       <c r="D22" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E22">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F22">
-        <v>1877</v>
+        <v>2285</v>
       </c>
       <c r="G22" t="s">
-        <v>75</v>
-      </c>
-      <c r="H22">
-        <v>400000</v>
+        <v>73</v>
       </c>
       <c r="I22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J22">
-        <v>83.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="K22">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="L22">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="M22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N22">
         <v>0</v>
       </c>
       <c r="O22">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="P22">
-        <v>40</v>
+        <v>38.8</v>
+      </c>
+      <c r="Q22">
+        <v>65.3</v>
+      </c>
+      <c r="R22">
+        <v>17</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22">
         <v>0</v>
@@ -3103,28 +3103,31 @@
         <v>52</v>
       </c>
       <c r="D23" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E23">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F23">
-        <v>2285</v>
+        <v>1133</v>
       </c>
       <c r="G23" t="s">
-        <v>74</v>
+        <v>73</v>
+      </c>
+      <c r="H23">
+        <v>1000000</v>
       </c>
       <c r="I23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J23">
-        <v>81.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K23">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="L23">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M23">
         <v>2</v>
@@ -3133,25 +3136,25 @@
         <v>0</v>
       </c>
       <c r="O23">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="P23">
-        <v>38.8</v>
+        <v>35</v>
       </c>
       <c r="Q23">
-        <v>65.3</v>
+        <v>81.2</v>
       </c>
       <c r="R23">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="S23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -3162,55 +3165,49 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
         <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E24">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F24">
-        <v>1133</v>
+        <v>2014</v>
       </c>
       <c r="G24" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H24">
-        <v>1000000</v>
+        <v>750000</v>
       </c>
       <c r="I24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J24">
-        <v>81.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K24">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="L24">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="M24">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>0</v>
       </c>
       <c r="O24">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="P24">
-        <v>35</v>
-      </c>
-      <c r="Q24">
-        <v>81.2</v>
-      </c>
-      <c r="R24">
-        <v>21</v>
+        <v>29.8</v>
       </c>
       <c r="S24">
         <v>1</v>
@@ -3230,58 +3227,58 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
         <v>54</v>
       </c>
       <c r="D25" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E25">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F25">
-        <v>2014</v>
+        <v>2238</v>
       </c>
       <c r="G25" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H25">
-        <v>750000</v>
+        <v>100000</v>
       </c>
       <c r="I25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J25">
-        <v>79.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="K25">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="L25">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="M25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="P25">
-        <v>29.8</v>
+        <v>34.4</v>
       </c>
       <c r="S25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25">
         <v>0</v>
@@ -3292,61 +3289,55 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
         <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E26">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F26">
-        <v>2238</v>
-      </c>
-      <c r="G26" t="s">
-        <v>80</v>
-      </c>
-      <c r="H26">
-        <v>100000</v>
+        <v>903</v>
       </c>
       <c r="I26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J26">
-        <v>79.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K26">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="L26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M26">
+        <v>3</v>
+      </c>
+      <c r="N26">
+        <v>66.7</v>
+      </c>
+      <c r="O26">
+        <v>0.03</v>
+      </c>
+      <c r="P26">
+        <v>37.5</v>
+      </c>
+      <c r="S26">
         <v>1</v>
       </c>
-      <c r="N26">
-        <v>100</v>
-      </c>
-      <c r="O26">
-        <v>0.08</v>
-      </c>
-      <c r="P26">
-        <v>34.4</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
       <c r="T26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3388,40 +3379,40 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:21">
@@ -3429,13 +3420,13 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E2">
         <v>33</v>
@@ -3444,13 +3435,13 @@
         <v>1988</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H2">
         <v>900000</v>
       </c>
       <c r="I2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J2">
         <v>92.5</v>
@@ -3488,10 +3479,10 @@
         <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
         <v>57</v>
@@ -3503,10 +3494,10 @@
         <v>2612</v>
       </c>
       <c r="G3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J3">
         <v>90.7</v>
@@ -3553,10 +3544,10 @@
         <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E4">
         <v>31</v>
@@ -3565,13 +3556,13 @@
         <v>1585</v>
       </c>
       <c r="G4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H4">
         <v>400000</v>
       </c>
       <c r="I4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J4">
         <v>88.3</v>
@@ -3618,10 +3609,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E5">
         <v>28</v>
@@ -3630,13 +3621,13 @@
         <v>1299</v>
       </c>
       <c r="G5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H5">
         <v>800000</v>
       </c>
       <c r="I5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J5">
         <v>88</v>
@@ -3674,10 +3665,10 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
         <v>59</v>
@@ -3692,7 +3683,7 @@
         <v>128</v>
       </c>
       <c r="I6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J6">
         <v>85</v>
@@ -3733,10 +3724,10 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E7">
         <v>24</v>
@@ -3748,7 +3739,7 @@
         <v>129</v>
       </c>
       <c r="I7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J7">
         <v>84.09999999999999</v>
@@ -3786,13 +3777,13 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E8">
         <v>31</v>
@@ -3801,13 +3792,13 @@
         <v>1645</v>
       </c>
       <c r="G8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H8">
         <v>600000</v>
       </c>
       <c r="I8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J8">
         <v>84.09999999999999</v>
@@ -3851,13 +3842,13 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E9">
         <v>29</v>
@@ -3866,10 +3857,10 @@
         <v>1236</v>
       </c>
       <c r="G9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J9">
         <v>83.09999999999999</v>
@@ -3913,10 +3904,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E10">
         <v>24</v>
@@ -3928,7 +3919,7 @@
         <v>130</v>
       </c>
       <c r="I10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J10">
         <v>82.09999999999999</v>
@@ -3966,10 +3957,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E11">
         <v>27</v>
@@ -3978,13 +3969,13 @@
         <v>2236</v>
       </c>
       <c r="G11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H11">
         <v>300000</v>
       </c>
       <c r="I11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J11">
         <v>80.8</v>
@@ -4031,10 +4022,10 @@
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12">
         <v>22</v>
@@ -4043,10 +4034,10 @@
         <v>1515</v>
       </c>
       <c r="G12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J12">
         <v>80.40000000000001</v>
@@ -4087,7 +4078,7 @@
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
         <v>57</v>
@@ -4099,13 +4090,13 @@
         <v>2420</v>
       </c>
       <c r="G13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H13">
         <v>400000</v>
       </c>
       <c r="I13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J13">
         <v>79.90000000000001</v>
@@ -4143,13 +4134,13 @@
         <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>126</v>
       </c>
       <c r="E14">
         <v>30</v>
@@ -4158,10 +4149,10 @@
         <v>1009</v>
       </c>
       <c r="G14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J14">
         <v>79.8</v>
@@ -4199,13 +4190,13 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E15">
         <v>30</v>
@@ -4214,10 +4205,10 @@
         <v>1733</v>
       </c>
       <c r="G15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J15">
         <v>77.7</v>
@@ -4261,13 +4252,13 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E16">
         <v>22</v>
@@ -4276,10 +4267,10 @@
         <v>1877</v>
       </c>
       <c r="G16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J16">
         <v>77.40000000000001</v>
@@ -4326,10 +4317,10 @@
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E17">
         <v>27</v>
@@ -4338,7 +4329,7 @@
         <v>1800</v>
       </c>
       <c r="G17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I17" t="s">
         <v>131</v>
@@ -4382,7 +4373,7 @@
         <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
         <v>59</v>
@@ -4394,10 +4385,10 @@
         <v>1438</v>
       </c>
       <c r="G18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J18">
         <v>74.8</v>
@@ -4444,7 +4435,7 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D19" t="s">
         <v>127</v>
@@ -4456,13 +4447,13 @@
         <v>908</v>
       </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H19">
         <v>250000</v>
       </c>
       <c r="I19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J19">
         <v>72.90000000000001</v>
@@ -4503,10 +4494,10 @@
         <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E20">
         <v>28</v>
@@ -4515,13 +4506,13 @@
         <v>2493</v>
       </c>
       <c r="G20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H20">
         <v>1200000</v>
       </c>
       <c r="I20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J20">
         <v>72.90000000000001</v>
@@ -4562,7 +4553,7 @@
         <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D21" t="s">
         <v>57</v>
@@ -4574,13 +4565,13 @@
         <v>2301</v>
       </c>
       <c r="G21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H21">
         <v>125000</v>
       </c>
       <c r="I21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J21">
         <v>72.09999999999999</v>
@@ -4627,10 +4618,10 @@
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E22">
         <v>28</v>
@@ -4639,13 +4630,13 @@
         <v>960</v>
       </c>
       <c r="G22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H22">
         <v>500000</v>
       </c>
       <c r="I22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J22">
         <v>71.5</v>
@@ -4692,10 +4683,10 @@
         <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E23">
         <v>27</v>
@@ -4704,10 +4695,10 @@
         <v>1728</v>
       </c>
       <c r="G23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J23">
         <v>69.90000000000001</v>
@@ -4754,10 +4745,10 @@
         <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E24">
         <v>33</v>
@@ -4766,7 +4757,7 @@
         <v>1408</v>
       </c>
       <c r="G24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H24">
         <v>2000000</v>
@@ -4813,10 +4804,10 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E25">
         <v>20</v>
@@ -4825,10 +4816,10 @@
         <v>1285</v>
       </c>
       <c r="G25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J25">
         <v>67.7</v>
@@ -4863,10 +4854,10 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
         <v>56</v>
@@ -4878,13 +4869,13 @@
         <v>1710</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H26">
         <v>450000</v>
       </c>
       <c r="I26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J26">
         <v>67.3</v>
@@ -4988,7 +4979,7 @@
         <v>133</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
         <v>134</v>
@@ -5003,7 +4994,7 @@
         <v>1682</v>
       </c>
       <c r="G2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -5053,7 +5044,7 @@
         <v>1920</v>
       </c>
       <c r="G3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -5088,7 +5079,7 @@
         <v>133</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
         <v>136</v>
@@ -5103,7 +5094,7 @@
         <v>1061</v>
       </c>
       <c r="G4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -5138,7 +5129,7 @@
         <v>133</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
         <v>137</v>
@@ -5153,7 +5144,7 @@
         <v>1914</v>
       </c>
       <c r="G5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -5203,13 +5194,13 @@
         <v>980</v>
       </c>
       <c r="G6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J6">
         <v>92.3</v>
@@ -5259,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J7">
         <v>88.8</v>
@@ -5288,7 +5279,7 @@
         <v>133</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
         <v>140</v>
@@ -5353,13 +5344,13 @@
         <v>933</v>
       </c>
       <c r="G9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J9">
         <v>85.2</v>
@@ -5459,7 +5450,7 @@
         <v>1500000</v>
       </c>
       <c r="I11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J11">
         <v>83.7</v>
@@ -5503,13 +5494,13 @@
         <v>1691</v>
       </c>
       <c r="G12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H12">
         <v>1200000</v>
       </c>
       <c r="I12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J12">
         <v>81</v>
@@ -5553,7 +5544,7 @@
         <v>1005</v>
       </c>
       <c r="G13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H13">
         <v>1000000</v>
@@ -5588,7 +5579,7 @@
         <v>133</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
         <v>146</v>
@@ -5653,13 +5644,13 @@
         <v>907</v>
       </c>
       <c r="G15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H15">
         <v>450000</v>
       </c>
       <c r="I15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J15">
         <v>80.40000000000001</v>
@@ -5809,7 +5800,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J18">
         <v>77.2</v>
@@ -5903,13 +5894,13 @@
         <v>1582</v>
       </c>
       <c r="G20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H20">
         <v>300000</v>
       </c>
       <c r="I20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J20">
         <v>76</v>
@@ -5959,7 +5950,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J21">
         <v>73.8</v>
@@ -6003,13 +5994,13 @@
         <v>1579</v>
       </c>
       <c r="G22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J22">
         <v>72.8</v>
@@ -6059,7 +6050,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J23">
         <v>71.7</v>
@@ -6103,7 +6094,7 @@
         <v>1913</v>
       </c>
       <c r="G24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H24">
         <v>2000000</v>
@@ -6159,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J25">
         <v>71.2</v>
@@ -6203,13 +6194,13 @@
         <v>1438</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H26">
         <v>900000</v>
       </c>
       <c r="I26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J26">
         <v>70.90000000000001</v>
@@ -6272,22 +6263,22 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -6295,7 +6286,7 @@
         <v>133</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
         <v>187</v>
@@ -6310,13 +6301,13 @@
         <v>1633</v>
       </c>
       <c r="G2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H2">
         <v>1000000</v>
       </c>
       <c r="I2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J2">
         <v>96.8</v>
@@ -6342,7 +6333,7 @@
         <v>133</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
         <v>188</v>
@@ -6357,13 +6348,13 @@
         <v>2261</v>
       </c>
       <c r="G3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H3">
         <v>250000</v>
       </c>
       <c r="I3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J3">
         <v>93.59999999999999</v>
@@ -6389,7 +6380,7 @@
         <v>133</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
         <v>189</v>
@@ -6410,7 +6401,7 @@
         <v>1500000</v>
       </c>
       <c r="I4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J4">
         <v>93.59999999999999</v>
@@ -6436,7 +6427,7 @@
         <v>133</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
         <v>190</v>
@@ -6451,13 +6442,13 @@
         <v>1549</v>
       </c>
       <c r="G5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H5">
         <v>400000</v>
       </c>
       <c r="I5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J5">
         <v>90.5</v>
@@ -6498,13 +6489,13 @@
         <v>1435</v>
       </c>
       <c r="G6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J6">
         <v>85.59999999999999</v>
@@ -6530,7 +6521,7 @@
         <v>133</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
         <v>192</v>
@@ -6545,13 +6536,13 @@
         <v>1694</v>
       </c>
       <c r="G7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H7">
         <v>100000</v>
       </c>
       <c r="I7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J7">
         <v>85.59999999999999</v>
@@ -6577,7 +6568,7 @@
         <v>133</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
         <v>193</v>
@@ -6592,13 +6583,13 @@
         <v>1711</v>
       </c>
       <c r="G8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H8">
         <v>100000</v>
       </c>
       <c r="I8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J8">
         <v>85.5</v>
@@ -6624,7 +6615,7 @@
         <v>133</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
         <v>194</v>
@@ -6639,7 +6630,7 @@
         <v>1708</v>
       </c>
       <c r="G9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H9">
         <v>850000</v>
@@ -6671,7 +6662,7 @@
         <v>133</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
         <v>195</v>
@@ -6686,13 +6677,13 @@
         <v>1618</v>
       </c>
       <c r="G10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J10">
         <v>83.7</v>
@@ -6718,7 +6709,7 @@
         <v>133</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
         <v>196</v>
@@ -6739,7 +6730,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J11">
         <v>82.3</v>
@@ -6812,7 +6803,7 @@
         <v>133</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
         <v>198</v>
@@ -6833,7 +6824,7 @@
         <v>2000000</v>
       </c>
       <c r="I13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J13">
         <v>78.90000000000001</v>
@@ -6859,7 +6850,7 @@
         <v>133</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
         <v>199</v>
@@ -6874,13 +6865,13 @@
         <v>1931</v>
       </c>
       <c r="G14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H14">
         <v>250000</v>
       </c>
       <c r="I14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J14">
         <v>78.7</v>
@@ -6927,7 +6918,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J15">
         <v>77.3</v>
@@ -7068,7 +7059,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J18">
         <v>67</v>
@@ -7094,7 +7085,7 @@
         <v>133</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
         <v>203</v>
@@ -7115,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J19">
         <v>65.2</v>
@@ -7156,13 +7147,13 @@
         <v>1868</v>
       </c>
       <c r="G20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H20">
         <v>1500000</v>
       </c>
       <c r="I20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J20">
         <v>64.7</v>
@@ -7188,7 +7179,7 @@
         <v>133</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C21" t="s">
         <v>205</v>
@@ -7203,13 +7194,13 @@
         <v>1962</v>
       </c>
       <c r="G21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H21">
         <v>1000000</v>
       </c>
       <c r="I21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J21">
         <v>64.2</v>
@@ -7256,7 +7247,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J22">
         <v>64.09999999999999</v>
@@ -7282,7 +7273,7 @@
         <v>133</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
         <v>207</v>
@@ -7300,7 +7291,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J23">
         <v>63.8</v>
@@ -7326,7 +7317,7 @@
         <v>133</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s">
         <v>208</v>
@@ -7341,13 +7332,13 @@
         <v>1620</v>
       </c>
       <c r="G24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H24">
         <v>1000000</v>
       </c>
       <c r="I24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J24">
         <v>62.5</v>
@@ -7373,7 +7364,7 @@
         <v>133</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
         <v>209</v>
@@ -7388,13 +7379,13 @@
         <v>1452</v>
       </c>
       <c r="G25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H25">
         <v>1000000</v>
       </c>
       <c r="I25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J25">
         <v>62</v>
@@ -7420,7 +7411,7 @@
         <v>133</v>
       </c>
       <c r="B26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s">
         <v>210</v>
@@ -7435,13 +7426,13 @@
         <v>1476</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H26">
         <v>1300000</v>
       </c>
       <c r="I26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J26">
         <v>61.4</v>
@@ -7542,7 +7533,7 @@
         <v>1422</v>
       </c>
       <c r="G2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -7595,7 +7586,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J3">
         <v>96</v>
@@ -7621,7 +7612,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -7639,13 +7630,13 @@
         <v>939</v>
       </c>
       <c r="G4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H4">
         <v>175000</v>
       </c>
       <c r="I4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J4">
         <v>96</v>
@@ -7689,13 +7680,13 @@
         <v>1589</v>
       </c>
       <c r="G5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J5">
         <v>95.59999999999999</v>
@@ -7721,7 +7712,7 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -7739,7 +7730,7 @@
         <v>1085</v>
       </c>
       <c r="G6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H6">
         <v>200000</v>
@@ -7774,7 +7765,7 @@
         <v>219</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
         <v>231</v>
@@ -7789,7 +7780,7 @@
         <v>1128</v>
       </c>
       <c r="G7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H7">
         <v>800000</v>
@@ -7824,7 +7815,7 @@
         <v>220</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
         <v>232</v>
@@ -7936,7 +7927,7 @@
         <v>2055</v>
       </c>
       <c r="G10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -7971,7 +7962,7 @@
         <v>221</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
         <v>235</v>
@@ -8036,7 +8027,7 @@
         <v>1602</v>
       </c>
       <c r="G12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -8086,7 +8077,7 @@
         <v>1809</v>
       </c>
       <c r="G13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -8136,7 +8127,7 @@
         <v>2172</v>
       </c>
       <c r="G14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -8171,7 +8162,7 @@
         <v>219</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
         <v>239</v>
@@ -8186,7 +8177,7 @@
         <v>1726</v>
       </c>
       <c r="G15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H15">
         <v>450000</v>
@@ -8236,13 +8227,13 @@
         <v>2156</v>
       </c>
       <c r="G16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J16">
         <v>94.09999999999999</v>
@@ -8289,7 +8280,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J17">
         <v>94.09999999999999</v>
@@ -8333,7 +8324,7 @@
         <v>1629</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -8415,7 +8406,7 @@
         <v>220</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
         <v>244</v>
@@ -8477,7 +8468,7 @@
         <v>1403</v>
       </c>
       <c r="G21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H21">
         <v>500000</v>
@@ -8530,7 +8521,7 @@
         <v>1500000</v>
       </c>
       <c r="I22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J22">
         <v>93.40000000000001</v>
@@ -8624,13 +8615,13 @@
         <v>1768</v>
       </c>
       <c r="G24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H24">
         <v>700000</v>
       </c>
       <c r="I24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J24">
         <v>93.40000000000001</v>
@@ -8721,7 +8712,7 @@
         <v>1049</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -8790,30 +8781,30 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
         <v>278</v>
@@ -8828,7 +8819,7 @@
         <v>1528</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H2">
         <v>500000</v>
@@ -8860,7 +8851,7 @@
         <v>221</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
         <v>279</v>
@@ -8904,7 +8895,7 @@
         <v>220</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
         <v>280</v>
@@ -8919,13 +8910,13 @@
         <v>2177</v>
       </c>
       <c r="G4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J4">
         <v>94.40000000000001</v>
@@ -8951,7 +8942,7 @@
         <v>222</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
         <v>281</v>
@@ -8966,7 +8957,7 @@
         <v>2099</v>
       </c>
       <c r="G5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H5">
         <v>75000</v>
@@ -8998,7 +8989,7 @@
         <v>218</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
         <v>282</v>
@@ -9013,7 +9004,7 @@
         <v>1911</v>
       </c>
       <c r="G6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -9045,7 +9036,7 @@
         <v>222</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
         <v>283</v>
@@ -9060,7 +9051,7 @@
         <v>2131</v>
       </c>
       <c r="G7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H7">
         <v>175000</v>
@@ -9107,13 +9098,13 @@
         <v>1133</v>
       </c>
       <c r="G8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J8">
         <v>92.09999999999999</v>
@@ -9154,7 +9145,7 @@
         <v>2232</v>
       </c>
       <c r="G9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -9186,7 +9177,7 @@
         <v>221</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
         <v>286</v>
@@ -9201,7 +9192,7 @@
         <v>1975</v>
       </c>
       <c r="G10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H10">
         <v>10000</v>
@@ -9233,7 +9224,7 @@
         <v>219</v>
       </c>
       <c r="B11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C11" t="s">
         <v>287</v>
@@ -9292,7 +9283,7 @@
         <v>1782</v>
       </c>
       <c r="G12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -9324,7 +9315,7 @@
         <v>217</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
         <v>289</v>
@@ -9339,13 +9330,13 @@
         <v>2059</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J13">
         <v>90.90000000000001</v>
@@ -9371,7 +9362,7 @@
         <v>222</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C14" t="s">
         <v>290</v>
@@ -9415,7 +9406,7 @@
         <v>224</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
         <v>291</v>
@@ -9459,7 +9450,7 @@
         <v>216</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
         <v>292</v>
@@ -9474,7 +9465,7 @@
         <v>1287</v>
       </c>
       <c r="G16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -9506,7 +9497,7 @@
         <v>216</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
         <v>293</v>
@@ -9553,7 +9544,7 @@
         <v>218</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
         <v>294</v>
@@ -9568,13 +9559,13 @@
         <v>1836</v>
       </c>
       <c r="G18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H18">
         <v>250000</v>
       </c>
       <c r="I18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J18">
         <v>89.59999999999999</v>
@@ -9600,7 +9591,7 @@
         <v>225</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
         <v>295</v>
@@ -9615,7 +9606,7 @@
         <v>1396</v>
       </c>
       <c r="G19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H19">
         <v>500000</v>
@@ -9753,13 +9744,13 @@
         <v>1124</v>
       </c>
       <c r="G22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J22">
         <v>88.7</v>
@@ -9785,7 +9776,7 @@
         <v>222</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C23" t="s">
         <v>299</v>
@@ -9800,7 +9791,7 @@
         <v>1595</v>
       </c>
       <c r="G23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H23">
         <v>375000</v>
@@ -9832,7 +9823,7 @@
         <v>218</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s">
         <v>300</v>
@@ -9847,7 +9838,7 @@
         <v>2016</v>
       </c>
       <c r="G24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H24">
         <v>350000</v>
@@ -9876,10 +9867,10 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
         <v>301</v>
@@ -9923,7 +9914,7 @@
         <v>220</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
         <v>302</v>
@@ -9938,7 +9929,7 @@
         <v>2209</v>
       </c>
       <c r="G26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H26">
         <v>400000</v>
@@ -10030,7 +10021,7 @@
         <v>328</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
         <v>341</v>
@@ -10045,13 +10036,13 @@
         <v>1382</v>
       </c>
       <c r="G2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H2">
         <v>2000000</v>
       </c>
       <c r="I2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J2">
         <v>95.2</v>
@@ -10095,13 +10086,13 @@
         <v>1326</v>
       </c>
       <c r="G3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J3">
         <v>95.09999999999999</v>
@@ -10130,7 +10121,7 @@
         <v>330</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
         <v>343</v>
@@ -10145,7 +10136,7 @@
         <v>3548</v>
       </c>
       <c r="G4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -10198,7 +10189,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J5">
         <v>93.90000000000001</v>
@@ -10277,7 +10268,7 @@
         <v>332</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
         <v>346</v>
@@ -10298,7 +10289,7 @@
         <v>1000000</v>
       </c>
       <c r="I7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J7">
         <v>93.59999999999999</v>
@@ -10348,7 +10339,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J8">
         <v>93.5</v>
@@ -10377,7 +10368,7 @@
         <v>333</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
         <v>348</v>
@@ -10392,13 +10383,13 @@
         <v>1683</v>
       </c>
       <c r="G9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J9">
         <v>92.90000000000001</v>
@@ -10495,7 +10486,7 @@
         <v>500000</v>
       </c>
       <c r="I11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J11">
         <v>92.59999999999999</v>
@@ -10539,13 +10530,13 @@
         <v>2019</v>
       </c>
       <c r="G12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H12">
         <v>800000</v>
       </c>
       <c r="I12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J12">
         <v>92.5</v>
@@ -10589,13 +10580,13 @@
         <v>1483</v>
       </c>
       <c r="G13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H13">
         <v>350000</v>
       </c>
       <c r="I13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J13">
         <v>92.5</v>
@@ -10639,7 +10630,7 @@
         <v>1295</v>
       </c>
       <c r="G14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -10689,13 +10680,13 @@
         <v>2691</v>
       </c>
       <c r="G15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J15">
         <v>91.8</v>
@@ -10739,13 +10730,13 @@
         <v>1202</v>
       </c>
       <c r="G16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J16">
         <v>91.7</v>
@@ -10792,7 +10783,7 @@
         <v>175000</v>
       </c>
       <c r="I17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J17">
         <v>91.7</v>
@@ -10821,7 +10812,7 @@
         <v>337</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
         <v>357</v>
@@ -10836,13 +10827,13 @@
         <v>1367</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H18">
         <v>1400000</v>
       </c>
       <c r="I18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J18">
         <v>91.5</v>
@@ -10989,7 +10980,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J21">
         <v>91</v>
@@ -11089,7 +11080,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J23">
         <v>90.40000000000001</v>
@@ -11168,7 +11159,7 @@
         <v>334</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
         <v>364</v>
@@ -11302,22 +11293,22 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -11393,7 +11384,7 @@
         <v>300000</v>
       </c>
       <c r="I3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J3">
         <v>94.09999999999999</v>
@@ -11440,7 +11431,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J4">
         <v>93.7</v>
@@ -11466,7 +11457,7 @@
         <v>394</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
         <v>401</v>
@@ -11513,7 +11504,7 @@
         <v>395</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
         <v>402</v>
@@ -11560,7 +11551,7 @@
         <v>330</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>403</v>
@@ -11575,7 +11566,7 @@
         <v>1947</v>
       </c>
       <c r="G7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H7">
         <v>1000000</v>
@@ -11607,7 +11598,7 @@
         <v>396</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
         <v>404</v>
@@ -11625,7 +11616,7 @@
         <v>200000</v>
       </c>
       <c r="I8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J8">
         <v>91.09999999999999</v>
@@ -11651,7 +11642,7 @@
         <v>397</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
         <v>405</v>
@@ -11666,13 +11657,13 @@
         <v>1172</v>
       </c>
       <c r="G9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H9">
         <v>100000</v>
       </c>
       <c r="I9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J9">
         <v>90.8</v>
@@ -11698,7 +11689,7 @@
         <v>330</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
         <v>406</v>
@@ -11713,13 +11704,13 @@
         <v>2833</v>
       </c>
       <c r="G10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J10">
         <v>90.7</v>
@@ -11745,7 +11736,7 @@
         <v>329</v>
       </c>
       <c r="B11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C11" t="s">
         <v>407</v>
@@ -11763,7 +11754,7 @@
         <v>200000</v>
       </c>
       <c r="I11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J11">
         <v>90.2</v>
@@ -11789,7 +11780,7 @@
         <v>397</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
         <v>408</v>
@@ -11810,7 +11801,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J12">
         <v>89.40000000000001</v>
@@ -11883,7 +11874,7 @@
         <v>328</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C14" t="s">
         <v>410</v>
@@ -11898,13 +11889,13 @@
         <v>3835</v>
       </c>
       <c r="G14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H14">
         <v>800000</v>
       </c>
       <c r="I14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J14">
         <v>88.3</v>
@@ -11930,7 +11921,7 @@
         <v>335</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
         <v>411</v>
@@ -11948,7 +11939,7 @@
         <v>175000</v>
       </c>
       <c r="I15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J15">
         <v>88.2</v>
@@ -11992,7 +11983,7 @@
         <v>850000</v>
       </c>
       <c r="I16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J16">
         <v>87.8</v>
@@ -12033,13 +12024,13 @@
         <v>1324</v>
       </c>
       <c r="G17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H17">
         <v>850000</v>
       </c>
       <c r="I17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J17">
         <v>87.40000000000001</v>
@@ -12065,7 +12056,7 @@
         <v>395</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
         <v>346</v>
@@ -12086,7 +12077,7 @@
         <v>250000</v>
       </c>
       <c r="I18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J18">
         <v>87.2</v>
@@ -12174,13 +12165,13 @@
         <v>1732</v>
       </c>
       <c r="G20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J20">
         <v>86.59999999999999</v>
@@ -12206,7 +12197,7 @@
         <v>333</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
         <v>416</v>
@@ -12221,7 +12212,7 @@
         <v>1395</v>
       </c>
       <c r="G21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H21">
         <v>450000</v>
@@ -12253,7 +12244,7 @@
         <v>337</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C22" t="s">
         <v>417</v>
@@ -12271,7 +12262,7 @@
         <v>400000</v>
       </c>
       <c r="I22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J22">
         <v>85.2</v>
@@ -12312,13 +12303,13 @@
         <v>1486</v>
       </c>
       <c r="G23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J23">
         <v>85.2</v>
@@ -12344,7 +12335,7 @@
         <v>337</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s">
         <v>419</v>
@@ -12359,13 +12350,13 @@
         <v>1533</v>
       </c>
       <c r="G24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H24">
         <v>1200000</v>
       </c>
       <c r="I24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J24">
         <v>85.09999999999999</v>
@@ -12438,7 +12429,7 @@
         <v>332</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
         <v>421</v>
@@ -12459,7 +12450,7 @@
         <v>400000</v>
       </c>
       <c r="I26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J26">
         <v>84.90000000000001</v>

--- a/Santa Cruz V2/listas/bola_parada_especialistas.xlsx
+++ b/Santa Cruz V2/listas/bola_parada_especialistas.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="443">
   <si>
     <t>liga</t>
   </si>
@@ -107,15 +107,15 @@
     <t>LD</t>
   </si>
   <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>LE</t>
+  </si>
+  <si>
     <t>MEI</t>
   </si>
   <si>
-    <t>CA</t>
-  </si>
-  <si>
-    <t>LE</t>
-  </si>
-  <si>
     <t>Rómulo Otero</t>
   </si>
   <si>
@@ -143,9 +143,6 @@
     <t>Maílton</t>
   </si>
   <si>
-    <t>Boschilia</t>
-  </si>
-  <si>
     <t>Daniel Penha</t>
   </si>
   <si>
@@ -170,12 +167,12 @@
     <t>Gegé</t>
   </si>
   <si>
+    <t>Jean Lucas</t>
+  </si>
+  <si>
     <t>Mikael Doka</t>
   </si>
   <si>
-    <t>Jean Lucas</t>
-  </si>
-  <si>
     <t>Dadá Belmonte</t>
   </si>
   <si>
@@ -191,6 +188,9 @@
     <t>Wesley Pinheiro</t>
   </si>
   <si>
+    <t>Gabriel Fuentes</t>
+  </si>
+  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -218,24 +218,24 @@
     <t>Fortaleza</t>
   </si>
   <si>
+    <t>Avaí</t>
+  </si>
+  <si>
+    <t>Ceará</t>
+  </si>
+  <si>
+    <t>Juventude</t>
+  </si>
+  <si>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>Goiás</t>
+  </si>
+  <si>
     <t>Operário-PR</t>
   </si>
   <si>
-    <t>Avaí</t>
-  </si>
-  <si>
-    <t>Ceará</t>
-  </si>
-  <si>
-    <t>Juventude</t>
-  </si>
-  <si>
-    <t>CRB</t>
-  </si>
-  <si>
-    <t>Goiás</t>
-  </si>
-  <si>
     <t>Atlético-GO</t>
   </si>
   <si>
@@ -254,325 +254,328 @@
     <t>2029-07-31</t>
   </si>
   <si>
+    <t>2028-12-31</t>
+  </si>
+  <si>
+    <t>2027-03-31</t>
+  </si>
+  <si>
+    <t>2028-08-31</t>
+  </si>
+  <si>
+    <t>Venezuela</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Brazil, Germany</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>indice_finalizador</t>
+  </si>
+  <si>
+    <t>Head goals</t>
+  </si>
+  <si>
+    <t>Head goals per 90</t>
+  </si>
+  <si>
+    <t>Aerial duels per 90</t>
+  </si>
+  <si>
+    <t>Aerial duels won, %</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>finalizador_2025</t>
+  </si>
+  <si>
+    <t>gols_cabeca_2025</t>
+  </si>
+  <si>
+    <t>gols_bp_2026</t>
+  </si>
+  <si>
+    <t>gols_bp_3t</t>
+  </si>
+  <si>
+    <t>gols_bp_cabeca_3t</t>
+  </si>
+  <si>
+    <t>xg_bp_3t</t>
+  </si>
+  <si>
+    <t>ZE</t>
+  </si>
+  <si>
+    <t>ZD</t>
+  </si>
+  <si>
+    <t>Luiz Otávio</t>
+  </si>
+  <si>
+    <t>Vilar</t>
+  </si>
+  <si>
+    <t>Alisson Safira</t>
+  </si>
+  <si>
+    <t>Matheus Bianqui</t>
+  </si>
+  <si>
+    <t>Yago Lincoln</t>
+  </si>
+  <si>
+    <t>Dudu</t>
+  </si>
+  <si>
+    <t>Messias</t>
+  </si>
+  <si>
+    <t>Gabriel Pinheiro</t>
+  </si>
+  <si>
+    <t>Kadu</t>
+  </si>
+  <si>
+    <t>Mikael</t>
+  </si>
+  <si>
+    <t>Paulo Vitor</t>
+  </si>
+  <si>
+    <t>Everton Morelli</t>
+  </si>
+  <si>
+    <t>Léo Índio</t>
+  </si>
+  <si>
+    <t>Benevenuto</t>
+  </si>
+  <si>
+    <t>Júlio César</t>
+  </si>
+  <si>
+    <t>J. Miritello</t>
+  </si>
+  <si>
+    <t>André Luiz</t>
+  </si>
+  <si>
+    <t>Léo Gomes</t>
+  </si>
+  <si>
+    <t>Perotti</t>
+  </si>
+  <si>
+    <t>Bruno José</t>
+  </si>
+  <si>
+    <t>Gustavo Coutinho</t>
+  </si>
+  <si>
+    <t>G. Mastriani</t>
+  </si>
+  <si>
+    <t>Kauan Cristtyan</t>
+  </si>
+  <si>
+    <t>Willean Lepo</t>
+  </si>
+  <si>
+    <t>Novorizontino</t>
+  </si>
+  <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
+    <t>Náutico</t>
+  </si>
+  <si>
+    <t>Ponte Preta</t>
+  </si>
+  <si>
+    <t>2030-06-30</t>
+  </si>
+  <si>
+    <t>2029-11-30</t>
+  </si>
+  <si>
+    <t>2026-12-15</t>
+  </si>
+  <si>
     <t>2027-11-30</t>
   </si>
   <si>
-    <t>2028-12-31</t>
-  </si>
-  <si>
-    <t>2027-03-31</t>
-  </si>
-  <si>
-    <t>Venezuela</t>
-  </si>
-  <si>
-    <t>Brazil</t>
-  </si>
-  <si>
-    <t>Paraguay</t>
-  </si>
-  <si>
-    <t>Ecuador</t>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Uruguay, Italy</t>
+  </si>
+  <si>
+    <t>Brasil A</t>
+  </si>
+  <si>
+    <t>R. Garro</t>
+  </si>
+  <si>
+    <t>Andreas Pereira</t>
+  </si>
+  <si>
+    <t>Giorgian de Arrascaeta</t>
+  </si>
+  <si>
+    <t>Matheus Pereira</t>
+  </si>
+  <si>
+    <t>Vitor Bueno</t>
+  </si>
+  <si>
+    <t>Luciano Juba</t>
+  </si>
+  <si>
+    <t>L. Esquivel</t>
+  </si>
+  <si>
+    <t>Pedro Gabriel</t>
+  </si>
+  <si>
+    <t>J. Rojas</t>
+  </si>
+  <si>
+    <t>Matheuzinho</t>
+  </si>
+  <si>
+    <t>Erick</t>
+  </si>
+  <si>
+    <t>Nuno Moreira</t>
+  </si>
+  <si>
+    <t>L. Acosta</t>
+  </si>
+  <si>
+    <t>Negueba</t>
+  </si>
+  <si>
+    <t>J. Piquerez</t>
+  </si>
+  <si>
+    <t>J. Carrascal</t>
+  </si>
+  <si>
+    <t>Keny Arroyo</t>
+  </si>
+  <si>
+    <t>R. Sosa</t>
+  </si>
+  <si>
+    <t>Danielzinho</t>
+  </si>
+  <si>
+    <t>Danilo</t>
+  </si>
+  <si>
+    <t>Lucas Ronier</t>
+  </si>
+  <si>
+    <t>Guilherme Arana</t>
+  </si>
+  <si>
+    <t>Alexandro Bernabei</t>
+  </si>
+  <si>
+    <t>Gabriel Bontempo</t>
+  </si>
+  <si>
+    <t>Renê</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
+    <t>Palmeiras</t>
+  </si>
+  <si>
+    <t>Flamengo</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Athletico Paranaense</t>
+  </si>
+  <si>
+    <t>Grêmio</t>
+  </si>
+  <si>
+    <t>Vasco da Gama</t>
+  </si>
+  <si>
+    <t>Vitória</t>
+  </si>
+  <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
+    <t>Coritiba</t>
+  </si>
+  <si>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>2029-12-31</t>
+  </si>
+  <si>
+    <t>2029-06-30</t>
+  </si>
+  <si>
+    <t>2028-06-30</t>
+  </si>
+  <si>
+    <t>2030-12-31</t>
+  </si>
+  <si>
+    <t>Argentina, Italy</t>
+  </si>
+  <si>
+    <t>Belgium, Brazil</t>
+  </si>
+  <si>
+    <t>Brazil, Portugal</t>
   </si>
   <si>
     <t>Brazil, Italy</t>
-  </si>
-  <si>
-    <t>Brazil, Germany</t>
-  </si>
-  <si>
-    <t>indice_finalizador</t>
-  </si>
-  <si>
-    <t>Head goals</t>
-  </si>
-  <si>
-    <t>Head goals per 90</t>
-  </si>
-  <si>
-    <t>Aerial duels per 90</t>
-  </si>
-  <si>
-    <t>Aerial duels won, %</t>
-  </si>
-  <si>
-    <t>Height</t>
-  </si>
-  <si>
-    <t>finalizador_2025</t>
-  </si>
-  <si>
-    <t>gols_cabeca_2025</t>
-  </si>
-  <si>
-    <t>gols_bp_2026</t>
-  </si>
-  <si>
-    <t>gols_bp_3t</t>
-  </si>
-  <si>
-    <t>gols_bp_cabeca_3t</t>
-  </si>
-  <si>
-    <t>xg_bp_3t</t>
-  </si>
-  <si>
-    <t>ZE</t>
-  </si>
-  <si>
-    <t>ZD</t>
-  </si>
-  <si>
-    <t>Luiz Otávio</t>
-  </si>
-  <si>
-    <t>Vilar</t>
-  </si>
-  <si>
-    <t>Alisson Safira</t>
-  </si>
-  <si>
-    <t>Matheus Bianqui</t>
-  </si>
-  <si>
-    <t>Yago Lincoln</t>
-  </si>
-  <si>
-    <t>Dudu</t>
-  </si>
-  <si>
-    <t>Messias</t>
-  </si>
-  <si>
-    <t>Gabriel Pinheiro</t>
-  </si>
-  <si>
-    <t>Kadu</t>
-  </si>
-  <si>
-    <t>Mikael</t>
-  </si>
-  <si>
-    <t>Paulo Vitor</t>
-  </si>
-  <si>
-    <t>Everton Morelli</t>
-  </si>
-  <si>
-    <t>Léo Índio</t>
-  </si>
-  <si>
-    <t>Benevenuto</t>
-  </si>
-  <si>
-    <t>Júlio César</t>
-  </si>
-  <si>
-    <t>J. Miritello</t>
-  </si>
-  <si>
-    <t>André Luiz</t>
-  </si>
-  <si>
-    <t>Léo Gomes</t>
-  </si>
-  <si>
-    <t>Perotti</t>
-  </si>
-  <si>
-    <t>Bruno José</t>
-  </si>
-  <si>
-    <t>Gustavo Coutinho</t>
-  </si>
-  <si>
-    <t>G. Mastriani</t>
-  </si>
-  <si>
-    <t>Kauan Cristtyan</t>
-  </si>
-  <si>
-    <t>Willean Lepo</t>
-  </si>
-  <si>
-    <t>Novorizontino</t>
-  </si>
-  <si>
-    <t>Vila Nova</t>
-  </si>
-  <si>
-    <t>Náutico</t>
-  </si>
-  <si>
-    <t>Ponte Preta</t>
-  </si>
-  <si>
-    <t>2030-06-30</t>
-  </si>
-  <si>
-    <t>2029-11-30</t>
-  </si>
-  <si>
-    <t>2026-12-15</t>
-  </si>
-  <si>
-    <t>Argentina</t>
-  </si>
-  <si>
-    <t>Uruguay, Italy</t>
-  </si>
-  <si>
-    <t>Brasil A</t>
-  </si>
-  <si>
-    <t>R. Garro</t>
-  </si>
-  <si>
-    <t>Andreas Pereira</t>
-  </si>
-  <si>
-    <t>Giorgian de Arrascaeta</t>
-  </si>
-  <si>
-    <t>Matheus Pereira</t>
-  </si>
-  <si>
-    <t>Vitor Bueno</t>
-  </si>
-  <si>
-    <t>Luciano Juba</t>
-  </si>
-  <si>
-    <t>L. Esquivel</t>
-  </si>
-  <si>
-    <t>Pedro Gabriel</t>
-  </si>
-  <si>
-    <t>J. Rojas</t>
-  </si>
-  <si>
-    <t>Matheuzinho</t>
-  </si>
-  <si>
-    <t>Erick</t>
-  </si>
-  <si>
-    <t>Nuno Moreira</t>
-  </si>
-  <si>
-    <t>L. Acosta</t>
-  </si>
-  <si>
-    <t>Negueba</t>
-  </si>
-  <si>
-    <t>J. Piquerez</t>
-  </si>
-  <si>
-    <t>J. Carrascal</t>
-  </si>
-  <si>
-    <t>Keny Arroyo</t>
-  </si>
-  <si>
-    <t>R. Sosa</t>
-  </si>
-  <si>
-    <t>Danielzinho</t>
-  </si>
-  <si>
-    <t>Danilo</t>
-  </si>
-  <si>
-    <t>Lucas Ronier</t>
-  </si>
-  <si>
-    <t>Guilherme Arana</t>
-  </si>
-  <si>
-    <t>Alexandro Bernabei</t>
-  </si>
-  <si>
-    <t>Gabriel Bontempo</t>
-  </si>
-  <si>
-    <t>Renê</t>
-  </si>
-  <si>
-    <t>Corinthians</t>
-  </si>
-  <si>
-    <t>Palmeiras</t>
-  </si>
-  <si>
-    <t>Flamengo</t>
-  </si>
-  <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Remo</t>
-  </si>
-  <si>
-    <t>Bahia</t>
-  </si>
-  <si>
-    <t>Athletico Paranaense</t>
-  </si>
-  <si>
-    <t>Grêmio</t>
-  </si>
-  <si>
-    <t>Vasco da Gama</t>
-  </si>
-  <si>
-    <t>Vitória</t>
-  </si>
-  <si>
-    <t>Fluminense</t>
-  </si>
-  <si>
-    <t>Mirassol</t>
-  </si>
-  <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
-    <t>Coritiba</t>
-  </si>
-  <si>
-    <t>Internacional</t>
-  </si>
-  <si>
-    <t>Santos</t>
-  </si>
-  <si>
-    <t>2029-12-31</t>
-  </si>
-  <si>
-    <t>2029-06-30</t>
-  </si>
-  <si>
-    <t>2028-06-30</t>
-  </si>
-  <si>
-    <t>2030-12-31</t>
-  </si>
-  <si>
-    <t>Argentina, Italy</t>
-  </si>
-  <si>
-    <t>Belgium, Brazil</t>
-  </si>
-  <si>
-    <t>Brazil, Portugal</t>
-  </si>
-  <si>
-    <t>Colombia</t>
   </si>
   <si>
     <t>Portugal</t>
@@ -2338,55 +2341,52 @@
         <v>65</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F11">
-        <v>2396</v>
+        <v>1313</v>
       </c>
       <c r="G11" t="s">
-        <v>77</v>
+        <v>72</v>
+      </c>
+      <c r="H11">
+        <v>750000</v>
       </c>
       <c r="I11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J11">
-        <v>89</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="K11">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="L11">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="M11">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="N11">
-        <v>47.1</v>
+        <v>20</v>
       </c>
       <c r="O11">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="P11">
-        <v>20</v>
-      </c>
-      <c r="Q11">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="R11">
-        <v>102</v>
+        <v>44.4</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
       <c r="T11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -2394,7 +2394,7 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
         <v>41</v>
@@ -2403,49 +2403,46 @@
         <v>66</v>
       </c>
       <c r="E12">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F12">
-        <v>1313</v>
+        <v>1761</v>
       </c>
       <c r="G12" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12">
-        <v>750000</v>
+        <v>77</v>
       </c>
       <c r="I12" t="s">
         <v>81</v>
       </c>
       <c r="J12">
-        <v>88.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="K12">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="L12">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N12">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="O12">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="P12">
-        <v>44.4</v>
+        <v>30.2</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -2456,52 +2453,61 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
         <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>1761</v>
+        <v>1569</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>72</v>
+      </c>
+      <c r="H13">
+        <v>500000</v>
       </c>
       <c r="I13" t="s">
         <v>81</v>
       </c>
       <c r="J13">
-        <v>88</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K13">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L13">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N13">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="O13">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="P13">
-        <v>30.2</v>
+        <v>46.4</v>
+      </c>
+      <c r="Q13">
+        <v>79.2</v>
+      </c>
+      <c r="R13">
+        <v>18</v>
       </c>
       <c r="S13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U13">
         <v>3</v>
@@ -2515,64 +2521,61 @@
         <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
         <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E14">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F14">
-        <v>1569</v>
+        <v>2186</v>
       </c>
       <c r="G14" t="s">
         <v>72</v>
       </c>
-      <c r="H14">
-        <v>500000</v>
-      </c>
       <c r="I14" t="s">
         <v>81</v>
       </c>
       <c r="J14">
-        <v>87.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="K14">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L14">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="M14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="O14">
         <v>0.11</v>
       </c>
       <c r="P14">
-        <v>46.4</v>
+        <v>32.3</v>
       </c>
       <c r="Q14">
-        <v>79.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R14">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -2583,64 +2586,67 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
         <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E15">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F15">
-        <v>2186</v>
+        <v>2301</v>
       </c>
       <c r="G15" t="s">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="H15">
+        <v>125000</v>
       </c>
       <c r="I15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J15">
-        <v>86.7</v>
+        <v>84.5</v>
       </c>
       <c r="K15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L15">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="M15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N15">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="O15">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="P15">
-        <v>32.3</v>
+        <v>32</v>
       </c>
       <c r="Q15">
-        <v>92.90000000000001</v>
+        <v>61</v>
       </c>
       <c r="R15">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="S15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U15">
         <v>2</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -2648,67 +2654,61 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
         <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E16">
         <v>29</v>
       </c>
       <c r="F16">
-        <v>2301</v>
+        <v>1941</v>
       </c>
       <c r="G16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H16">
-        <v>125000</v>
+        <v>900000</v>
       </c>
       <c r="I16" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="J16">
-        <v>84.5</v>
+        <v>84.2</v>
       </c>
       <c r="K16">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>17</v>
       </c>
       <c r="M16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N16">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="O16">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="P16">
-        <v>32</v>
-      </c>
-      <c r="Q16">
-        <v>61</v>
-      </c>
-      <c r="R16">
-        <v>6</v>
+        <v>48.3</v>
       </c>
       <c r="S16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2728,13 +2728,13 @@
         <v>29</v>
       </c>
       <c r="F17">
-        <v>1941</v>
+        <v>1435</v>
       </c>
       <c r="G17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H17">
-        <v>900000</v>
+        <v>1000000</v>
       </c>
       <c r="I17" t="s">
         <v>81</v>
@@ -2743,34 +2743,34 @@
         <v>84.2</v>
       </c>
       <c r="K17">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L17">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M17">
+        <v>9</v>
+      </c>
+      <c r="N17">
+        <v>11.1</v>
+      </c>
+      <c r="O17">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P17">
+        <v>36.4</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
         <v>3</v>
       </c>
-      <c r="N17">
-        <v>66.7</v>
-      </c>
-      <c r="O17">
-        <v>0.08</v>
-      </c>
-      <c r="P17">
-        <v>48.3</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
       <c r="U17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -2778,61 +2778,67 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
         <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E18">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F18">
-        <v>1435</v>
+        <v>1015</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H18">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="I18" t="s">
         <v>81</v>
       </c>
       <c r="J18">
-        <v>84.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K18">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L18">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M18">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N18">
-        <v>11.1</v>
+        <v>50</v>
       </c>
       <c r="O18">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="P18">
-        <v>36.4</v>
+        <v>21</v>
+      </c>
+      <c r="Q18">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="R18">
+        <v>97</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V18">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -2840,67 +2846,61 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
         <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E19">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F19">
-        <v>1015</v>
+        <v>1972</v>
       </c>
       <c r="G19" t="s">
         <v>72</v>
       </c>
       <c r="H19">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="I19" t="s">
         <v>81</v>
       </c>
       <c r="J19">
-        <v>83.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K19">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="L19">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="M19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N19">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="P19">
-        <v>21</v>
-      </c>
-      <c r="Q19">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="R19">
-        <v>97</v>
+        <v>28.1</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19">
         <v>1</v>
       </c>
       <c r="V19">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -2914,7 +2914,7 @@
         <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E20">
         <v>26</v>
@@ -2970,58 +2970,61 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
         <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E21">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F21">
-        <v>1972</v>
+        <v>2285</v>
       </c>
       <c r="G21" t="s">
-        <v>72</v>
-      </c>
-      <c r="H21">
-        <v>250000</v>
+        <v>73</v>
       </c>
       <c r="I21" t="s">
         <v>81</v>
       </c>
       <c r="J21">
-        <v>83.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="K21">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="L21">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="M21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N21">
         <v>0</v>
       </c>
       <c r="O21">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="P21">
-        <v>28.1</v>
+        <v>38.8</v>
+      </c>
+      <c r="Q21">
+        <v>65.3</v>
+      </c>
+      <c r="R21">
+        <v>17</v>
       </c>
       <c r="S21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -3038,28 +3041,31 @@
         <v>51</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E22">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F22">
-        <v>2285</v>
+        <v>1133</v>
       </c>
       <c r="G22" t="s">
         <v>73</v>
       </c>
+      <c r="H22">
+        <v>1000000</v>
+      </c>
       <c r="I22" t="s">
         <v>81</v>
       </c>
       <c r="J22">
-        <v>81.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K22">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="L22">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M22">
         <v>2</v>
@@ -3068,25 +3074,25 @@
         <v>0</v>
       </c>
       <c r="O22">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="P22">
-        <v>38.8</v>
+        <v>35</v>
       </c>
       <c r="Q22">
-        <v>65.3</v>
+        <v>81.2</v>
       </c>
       <c r="R22">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="S22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V22">
         <v>0</v>
@@ -3097,55 +3103,49 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
         <v>52</v>
       </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E23">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F23">
-        <v>1133</v>
+        <v>2014</v>
       </c>
       <c r="G23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H23">
-        <v>1000000</v>
+        <v>750000</v>
       </c>
       <c r="I23" t="s">
         <v>81</v>
       </c>
       <c r="J23">
-        <v>81.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K23">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="L23">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="M23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>0</v>
       </c>
       <c r="O23">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="P23">
-        <v>35</v>
-      </c>
-      <c r="Q23">
-        <v>81.2</v>
-      </c>
-      <c r="R23">
-        <v>21</v>
+        <v>29.8</v>
       </c>
       <c r="S23">
         <v>1</v>
@@ -3165,58 +3165,58 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C24" t="s">
         <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="E24">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F24">
-        <v>2014</v>
+        <v>2238</v>
       </c>
       <c r="G24" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H24">
-        <v>750000</v>
+        <v>100000</v>
       </c>
       <c r="I24" t="s">
         <v>81</v>
       </c>
       <c r="J24">
-        <v>79.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="K24">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="L24">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="M24">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="P24">
-        <v>29.8</v>
+        <v>34.4</v>
       </c>
       <c r="S24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24">
         <v>0</v>
@@ -3227,61 +3227,55 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
         <v>54</v>
       </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E25">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F25">
-        <v>2238</v>
-      </c>
-      <c r="G25" t="s">
-        <v>79</v>
-      </c>
-      <c r="H25">
-        <v>100000</v>
+        <v>903</v>
       </c>
       <c r="I25" t="s">
         <v>81</v>
       </c>
       <c r="J25">
-        <v>79.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K25">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="L25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M25">
+        <v>3</v>
+      </c>
+      <c r="N25">
+        <v>66.7</v>
+      </c>
+      <c r="O25">
+        <v>0.03</v>
+      </c>
+      <c r="P25">
+        <v>37.5</v>
+      </c>
+      <c r="S25">
         <v>1</v>
       </c>
-      <c r="N25">
-        <v>100</v>
-      </c>
-      <c r="O25">
-        <v>0.08</v>
-      </c>
-      <c r="P25">
-        <v>34.4</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
       <c r="T25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -3289,55 +3283,61 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
         <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E26">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F26">
-        <v>903</v>
+        <v>1162</v>
+      </c>
+      <c r="G26" t="s">
+        <v>79</v>
+      </c>
+      <c r="H26">
+        <v>1800000</v>
       </c>
       <c r="I26" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J26">
-        <v>78.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K26">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L26">
         <v>5</v>
       </c>
       <c r="M26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N26">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="P26">
-        <v>37.5</v>
+        <v>37.2</v>
       </c>
       <c r="S26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3426,7 +3426,7 @@
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E2">
         <v>33</v>
@@ -3541,13 +3541,13 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
         <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E4">
         <v>31</v>
@@ -3783,7 +3783,7 @@
         <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E8">
         <v>31</v>
@@ -3848,7 +3848,7 @@
         <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E9">
         <v>29</v>
@@ -3907,7 +3907,7 @@
         <v>108</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E10">
         <v>24</v>
@@ -3954,13 +3954,13 @@
         <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
         <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E11">
         <v>27</v>
@@ -3969,7 +3969,7 @@
         <v>2236</v>
       </c>
       <c r="G11" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="H11">
         <v>300000</v>
@@ -4025,7 +4025,7 @@
         <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E12">
         <v>22</v>
@@ -4090,7 +4090,7 @@
         <v>2420</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H13">
         <v>400000</v>
@@ -4258,7 +4258,7 @@
         <v>114</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E16">
         <v>22</v>
@@ -4314,7 +4314,7 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
         <v>115</v>
@@ -4332,7 +4332,7 @@
         <v>72</v>
       </c>
       <c r="I17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J17">
         <v>76.40000000000001</v>
@@ -4491,7 +4491,7 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
         <v>118</v>
@@ -4550,10 +4550,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s">
         <v>57</v>
@@ -4571,7 +4571,7 @@
         <v>125000</v>
       </c>
       <c r="I21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J21">
         <v>72.09999999999999</v>
@@ -4680,7 +4680,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
         <v>120</v>
@@ -4742,7 +4742,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C24" t="s">
         <v>121</v>
@@ -4763,7 +4763,7 @@
         <v>2000000</v>
       </c>
       <c r="I24" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J24">
         <v>68.59999999999999</v>
@@ -4801,7 +4801,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
         <v>122</v>
@@ -4976,16 +4976,16 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E2">
         <v>28</v>
@@ -4994,13 +4994,13 @@
         <v>1682</v>
       </c>
       <c r="G2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J2">
         <v>96.2</v>
@@ -5026,16 +5026,16 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E3">
         <v>30</v>
@@ -5044,13 +5044,13 @@
         <v>1920</v>
       </c>
       <c r="G3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J3">
         <v>95.3</v>
@@ -5076,16 +5076,16 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E4">
         <v>32</v>
@@ -5094,13 +5094,13 @@
         <v>1061</v>
       </c>
       <c r="G4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J4">
         <v>94</v>
@@ -5126,16 +5126,16 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E5">
         <v>30</v>
@@ -5144,13 +5144,13 @@
         <v>1914</v>
       </c>
       <c r="G5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J5">
         <v>92.3</v>
@@ -5176,16 +5176,16 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E6">
         <v>31</v>
@@ -5200,7 +5200,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>84</v>
+        <v>184</v>
       </c>
       <c r="J6">
         <v>92.3</v>
@@ -5226,16 +5226,16 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E7">
         <v>26</v>
@@ -5244,7 +5244,7 @@
         <v>1736</v>
       </c>
       <c r="G7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -5276,16 +5276,16 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s">
         <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E8">
         <v>24</v>
@@ -5294,13 +5294,13 @@
         <v>1456</v>
       </c>
       <c r="G8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J8">
         <v>87.40000000000001</v>
@@ -5326,16 +5326,16 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E9">
         <v>19</v>
@@ -5344,7 +5344,7 @@
         <v>933</v>
       </c>
       <c r="G9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -5376,16 +5376,16 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E10">
         <v>23</v>
@@ -5394,13 +5394,13 @@
         <v>934</v>
       </c>
       <c r="G10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J10">
         <v>83.8</v>
@@ -5426,16 +5426,16 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E11">
         <v>28</v>
@@ -5444,7 +5444,7 @@
         <v>1433</v>
       </c>
       <c r="G11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H11">
         <v>1500000</v>
@@ -5476,16 +5476,16 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B12" t="s">
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E12">
         <v>28</v>
@@ -5494,7 +5494,7 @@
         <v>1691</v>
       </c>
       <c r="G12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H12">
         <v>1200000</v>
@@ -5526,16 +5526,16 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B13" t="s">
         <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E13">
         <v>27</v>
@@ -5550,7 +5550,7 @@
         <v>1000000</v>
       </c>
       <c r="I13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J13">
         <v>80.7</v>
@@ -5576,16 +5576,16 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E14">
         <v>32</v>
@@ -5594,13 +5594,13 @@
         <v>1315</v>
       </c>
       <c r="G14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J14">
         <v>80.59999999999999</v>
@@ -5626,16 +5626,16 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B15" t="s">
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E15">
         <v>26</v>
@@ -5676,16 +5676,16 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E16">
         <v>27</v>
@@ -5694,13 +5694,13 @@
         <v>948</v>
       </c>
       <c r="G16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J16">
         <v>79.3</v>
@@ -5726,16 +5726,16 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s">
         <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E17">
         <v>28</v>
@@ -5744,13 +5744,13 @@
         <v>957</v>
       </c>
       <c r="G17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J17">
         <v>78.7</v>
@@ -5776,16 +5776,16 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E18">
         <v>20</v>
@@ -5794,7 +5794,7 @@
         <v>1196</v>
       </c>
       <c r="G18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -5826,16 +5826,16 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E19">
         <v>26</v>
@@ -5850,7 +5850,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J19">
         <v>76.2</v>
@@ -5876,16 +5876,16 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B20" t="s">
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E20">
         <v>31</v>
@@ -5926,16 +5926,16 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E21">
         <v>25</v>
@@ -5944,7 +5944,7 @@
         <v>1495</v>
       </c>
       <c r="G21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -5976,16 +5976,16 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -6026,16 +6026,16 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E23">
         <v>29</v>
@@ -6044,7 +6044,7 @@
         <v>979</v>
       </c>
       <c r="G23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -6076,16 +6076,16 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B24" t="s">
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E24">
         <v>25</v>
@@ -6094,13 +6094,13 @@
         <v>1913</v>
       </c>
       <c r="G24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H24">
         <v>2000000</v>
       </c>
       <c r="I24" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J24">
         <v>71.2</v>
@@ -6126,16 +6126,16 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B25" t="s">
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D25" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E25">
         <v>21</v>
@@ -6144,7 +6144,7 @@
         <v>1392</v>
       </c>
       <c r="G25" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -6176,16 +6176,16 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E26">
         <v>33</v>
@@ -6283,16 +6283,16 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B2" t="s">
         <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E2">
         <v>31</v>
@@ -6330,16 +6330,16 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B3" t="s">
         <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E3">
         <v>28</v>
@@ -6377,16 +6377,16 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E4">
         <v>29</v>
@@ -6395,7 +6395,7 @@
         <v>920</v>
       </c>
       <c r="G4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H4">
         <v>1500000</v>
@@ -6424,16 +6424,16 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s">
         <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E5">
         <v>22</v>
@@ -6448,7 +6448,7 @@
         <v>400000</v>
       </c>
       <c r="I5" t="s">
-        <v>84</v>
+        <v>184</v>
       </c>
       <c r="J5">
         <v>90.5</v>
@@ -6471,16 +6471,16 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E6">
         <v>22</v>
@@ -6518,16 +6518,16 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
         <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E7">
         <v>29</v>
@@ -6536,7 +6536,7 @@
         <v>1694</v>
       </c>
       <c r="G7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H7">
         <v>100000</v>
@@ -6565,16 +6565,16 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s">
         <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E8">
         <v>29</v>
@@ -6583,7 +6583,7 @@
         <v>1711</v>
       </c>
       <c r="G8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H8">
         <v>100000</v>
@@ -6612,16 +6612,16 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s">
         <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E9">
         <v>29</v>
@@ -6636,7 +6636,7 @@
         <v>850000</v>
       </c>
       <c r="I9" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J9">
         <v>83.90000000000001</v>
@@ -6659,16 +6659,16 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B10" t="s">
         <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E10">
         <v>30</v>
@@ -6677,7 +6677,7 @@
         <v>1618</v>
       </c>
       <c r="G10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -6706,16 +6706,16 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B11" t="s">
         <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E11">
         <v>21</v>
@@ -6724,7 +6724,7 @@
         <v>1323</v>
       </c>
       <c r="G11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -6753,16 +6753,16 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E12">
         <v>25</v>
@@ -6771,13 +6771,13 @@
         <v>1622</v>
       </c>
       <c r="G12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J12">
         <v>80.3</v>
@@ -6800,16 +6800,16 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E13">
         <v>25</v>
@@ -6818,7 +6818,7 @@
         <v>2021</v>
       </c>
       <c r="G13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H13">
         <v>2000000</v>
@@ -6847,16 +6847,16 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B14" t="s">
         <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D14" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E14">
         <v>27</v>
@@ -6894,16 +6894,16 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E15">
         <v>22</v>
@@ -6912,7 +6912,7 @@
         <v>1184</v>
       </c>
       <c r="G15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -6941,16 +6941,16 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E16">
         <v>29</v>
@@ -6959,13 +6959,13 @@
         <v>1082</v>
       </c>
       <c r="G16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J16">
         <v>76.5</v>
@@ -6988,16 +6988,16 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E17">
         <v>24</v>
@@ -7006,13 +7006,13 @@
         <v>1109</v>
       </c>
       <c r="G17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J17">
         <v>70.7</v>
@@ -7035,16 +7035,16 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s">
         <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E18">
         <v>26</v>
@@ -7053,7 +7053,7 @@
         <v>1133</v>
       </c>
       <c r="G18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -7082,16 +7082,16 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" t="s">
         <v>99</v>
       </c>
       <c r="C19" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E19">
         <v>30</v>
@@ -7100,7 +7100,7 @@
         <v>2013</v>
       </c>
       <c r="G19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -7129,16 +7129,16 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E20">
         <v>31</v>
@@ -7176,16 +7176,16 @@
     </row>
     <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B21" t="s">
         <v>98</v>
       </c>
       <c r="C21" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E21">
         <v>33</v>
@@ -7223,16 +7223,16 @@
     </row>
     <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E22">
         <v>24</v>
@@ -7241,7 +7241,7 @@
         <v>1398</v>
       </c>
       <c r="G22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -7270,16 +7270,16 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B23" t="s">
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D23" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E23">
         <v>28</v>
@@ -7314,16 +7314,16 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B24" t="s">
         <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D24" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E24">
         <v>26</v>
@@ -7332,7 +7332,7 @@
         <v>1620</v>
       </c>
       <c r="G24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H24">
         <v>1000000</v>
@@ -7361,16 +7361,16 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B25" t="s">
         <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E25">
         <v>29</v>
@@ -7379,7 +7379,7 @@
         <v>1452</v>
       </c>
       <c r="G25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H25">
         <v>1000000</v>
@@ -7408,16 +7408,16 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" t="s">
         <v>98</v>
       </c>
       <c r="C26" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E26">
         <v>32</v>
@@ -7515,16 +7515,16 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E2">
         <v>19</v>
@@ -7539,7 +7539,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J2">
         <v>96.3</v>
@@ -7565,16 +7565,16 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E3">
         <v>31</v>
@@ -7618,10 +7618,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E4">
         <v>32</v>
@@ -7662,16 +7662,16 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E5">
         <v>32</v>
@@ -7718,10 +7718,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E6">
         <v>28</v>
@@ -7736,7 +7736,7 @@
         <v>200000</v>
       </c>
       <c r="I6" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J6">
         <v>95.3</v>
@@ -7762,16 +7762,16 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E7">
         <v>33</v>
@@ -7786,7 +7786,7 @@
         <v>800000</v>
       </c>
       <c r="I7" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J7">
         <v>95.3</v>
@@ -7812,16 +7812,16 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E8">
         <v>21</v>
@@ -7833,7 +7833,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J8">
         <v>95</v>
@@ -7859,16 +7859,16 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E9">
         <v>30</v>
@@ -7877,13 +7877,13 @@
         <v>1478</v>
       </c>
       <c r="G9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J9">
         <v>94.90000000000001</v>
@@ -7909,16 +7909,16 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E10">
         <v>28</v>
@@ -7927,13 +7927,13 @@
         <v>2055</v>
       </c>
       <c r="G10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J10">
         <v>94.5</v>
@@ -7959,16 +7959,16 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E11">
         <v>27</v>
@@ -7977,13 +7977,13 @@
         <v>1510</v>
       </c>
       <c r="G11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J11">
         <v>94.40000000000001</v>
@@ -8009,16 +8009,16 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E12">
         <v>30</v>
@@ -8027,13 +8027,13 @@
         <v>1602</v>
       </c>
       <c r="G12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J12">
         <v>94.40000000000001</v>
@@ -8059,16 +8059,16 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E13">
         <v>29</v>
@@ -8083,7 +8083,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J13">
         <v>94.2</v>
@@ -8109,16 +8109,16 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B14" t="s">
         <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E14">
         <v>24</v>
@@ -8133,7 +8133,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J14">
         <v>94.2</v>
@@ -8159,16 +8159,16 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D15" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E15">
         <v>24</v>
@@ -8183,7 +8183,7 @@
         <v>450000</v>
       </c>
       <c r="I15" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J15">
         <v>94.09999999999999</v>
@@ -8209,16 +8209,16 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B16" t="s">
         <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D16" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E16">
         <v>23</v>
@@ -8259,16 +8259,16 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E17">
         <v>27</v>
@@ -8306,16 +8306,16 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E18">
         <v>27</v>
@@ -8330,7 +8330,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J18">
         <v>93.90000000000001</v>
@@ -8356,16 +8356,16 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D19" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E19">
         <v>30</v>
@@ -8377,7 +8377,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J19">
         <v>93.8</v>
@@ -8403,16 +8403,16 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D20" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E20">
         <v>23</v>
@@ -8424,7 +8424,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J20">
         <v>93.7</v>
@@ -8450,16 +8450,16 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D21" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E21">
         <v>27</v>
@@ -8474,7 +8474,7 @@
         <v>500000</v>
       </c>
       <c r="I21" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J21">
         <v>93.7</v>
@@ -8500,16 +8500,16 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D22" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E22">
         <v>31</v>
@@ -8547,16 +8547,16 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D23" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -8565,13 +8565,13 @@
         <v>1700</v>
       </c>
       <c r="G23" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J23">
         <v>93.40000000000001</v>
@@ -8597,16 +8597,16 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D24" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -8647,16 +8647,16 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B25" t="s">
         <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -8668,7 +8668,7 @@
         <v>375000</v>
       </c>
       <c r="I25" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J25">
         <v>93.2</v>
@@ -8694,16 +8694,16 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B26" t="s">
         <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D26" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E26">
         <v>24</v>
@@ -8718,7 +8718,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J26">
         <v>93.09999999999999</v>
@@ -8807,10 +8807,10 @@
         <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E2">
         <v>30</v>
@@ -8825,7 +8825,7 @@
         <v>500000</v>
       </c>
       <c r="I2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J2">
         <v>96.8</v>
@@ -8848,16 +8848,16 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B3" t="s">
         <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E3">
         <v>31</v>
@@ -8869,7 +8869,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J3">
         <v>95.09999999999999</v>
@@ -8892,16 +8892,16 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B4" t="s">
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E4">
         <v>22</v>
@@ -8939,16 +8939,16 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B5" t="s">
         <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E5">
         <v>30</v>
@@ -8963,7 +8963,7 @@
         <v>75000</v>
       </c>
       <c r="I5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J5">
         <v>94.3</v>
@@ -8986,16 +8986,16 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B6" t="s">
         <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E6">
         <v>24</v>
@@ -9010,7 +9010,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J6">
         <v>92.40000000000001</v>
@@ -9033,16 +9033,16 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B7" t="s">
         <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E7">
         <v>30</v>
@@ -9057,7 +9057,7 @@
         <v>175000</v>
       </c>
       <c r="I7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J7">
         <v>92.3</v>
@@ -9080,16 +9080,16 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E8">
         <v>30</v>
@@ -9127,16 +9127,16 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E9">
         <v>28</v>
@@ -9151,7 +9151,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J9">
         <v>92</v>
@@ -9174,16 +9174,16 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B10" t="s">
         <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E10">
         <v>29</v>
@@ -9198,7 +9198,7 @@
         <v>10000</v>
       </c>
       <c r="I10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J10">
         <v>91.59999999999999</v>
@@ -9221,16 +9221,16 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B11" t="s">
         <v>99</v>
       </c>
       <c r="C11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E11">
         <v>31</v>
@@ -9242,7 +9242,7 @@
         <v>75000</v>
       </c>
       <c r="I11" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J11">
         <v>91.3</v>
@@ -9265,16 +9265,16 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E12">
         <v>30</v>
@@ -9289,7 +9289,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J12">
         <v>91.09999999999999</v>
@@ -9312,16 +9312,16 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B13" t="s">
         <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E13">
         <v>30</v>
@@ -9359,16 +9359,16 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B14" t="s">
         <v>99</v>
       </c>
       <c r="C14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E14">
         <v>24</v>
@@ -9380,7 +9380,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J14">
         <v>90.8</v>
@@ -9403,16 +9403,16 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B15" t="s">
         <v>99</v>
       </c>
       <c r="C15" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D15" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E15">
         <v>33</v>
@@ -9424,7 +9424,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J15">
         <v>90.8</v>
@@ -9447,16 +9447,16 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B16" t="s">
         <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D16" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E16">
         <v>25</v>
@@ -9471,7 +9471,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J16">
         <v>90.5</v>
@@ -9494,16 +9494,16 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B17" t="s">
         <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D17" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E17">
         <v>26</v>
@@ -9512,13 +9512,13 @@
         <v>2307</v>
       </c>
       <c r="G17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J17">
         <v>89.7</v>
@@ -9541,16 +9541,16 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B18" t="s">
         <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D18" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E18">
         <v>25</v>
@@ -9588,16 +9588,16 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B19" t="s">
         <v>99</v>
       </c>
       <c r="C19" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D19" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E19">
         <v>31</v>
@@ -9612,7 +9612,7 @@
         <v>500000</v>
       </c>
       <c r="I19" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J19">
         <v>89.3</v>
@@ -9635,16 +9635,16 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D20" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E20">
         <v>29</v>
@@ -9653,13 +9653,13 @@
         <v>1343</v>
       </c>
       <c r="G20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J20">
         <v>88.90000000000001</v>
@@ -9682,16 +9682,16 @@
     </row>
     <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D21" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E21">
         <v>24</v>
@@ -9703,7 +9703,7 @@
         <v>400000</v>
       </c>
       <c r="I21" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J21">
         <v>88.8</v>
@@ -9726,16 +9726,16 @@
     </row>
     <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D22" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E22">
         <v>26</v>
@@ -9773,16 +9773,16 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s">
         <v>98</v>
       </c>
       <c r="C23" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D23" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E23">
         <v>32</v>
@@ -9797,7 +9797,7 @@
         <v>375000</v>
       </c>
       <c r="I23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J23">
         <v>88.7</v>
@@ -9820,16 +9820,16 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s">
         <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D24" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E24">
         <v>27</v>
@@ -9844,7 +9844,7 @@
         <v>350000</v>
       </c>
       <c r="I24" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J24">
         <v>88.3</v>
@@ -9873,10 +9873,10 @@
         <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D25" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E25">
         <v>25</v>
@@ -9888,7 +9888,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J25">
         <v>88.09999999999999</v>
@@ -9911,16 +9911,16 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B26" t="s">
         <v>99</v>
       </c>
       <c r="C26" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D26" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E26">
         <v>29</v>
@@ -9935,7 +9935,7 @@
         <v>400000</v>
       </c>
       <c r="I26" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J26">
         <v>88</v>
@@ -10018,16 +10018,16 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E2">
         <v>32</v>
@@ -10068,16 +10068,16 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E3">
         <v>25</v>
@@ -10086,7 +10086,7 @@
         <v>1326</v>
       </c>
       <c r="G3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -10118,16 +10118,16 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E4">
         <v>29</v>
@@ -10142,7 +10142,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J4">
         <v>94.8</v>
@@ -10168,16 +10168,16 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E5">
         <v>30</v>
@@ -10215,16 +10215,16 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E6">
         <v>29</v>
@@ -10233,13 +10233,13 @@
         <v>3557</v>
       </c>
       <c r="G6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H6">
         <v>1800000</v>
       </c>
       <c r="I6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J6">
         <v>93.8</v>
@@ -10265,16 +10265,16 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E7">
         <v>25</v>
@@ -10283,7 +10283,7 @@
         <v>1413</v>
       </c>
       <c r="G7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H7">
         <v>1000000</v>
@@ -10315,16 +10315,16 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D8" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E8">
         <v>23</v>
@@ -10333,7 +10333,7 @@
         <v>2899</v>
       </c>
       <c r="G8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -10365,16 +10365,16 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E9">
         <v>28</v>
@@ -10415,16 +10415,16 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E10">
         <v>30</v>
@@ -10433,13 +10433,13 @@
         <v>2529</v>
       </c>
       <c r="G10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H10">
         <v>600000</v>
       </c>
       <c r="I10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J10">
         <v>92.59999999999999</v>
@@ -10465,16 +10465,16 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E11">
         <v>32</v>
@@ -10512,16 +10512,16 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D12" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E12">
         <v>31</v>
@@ -10562,16 +10562,16 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B13" t="s">
         <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E13">
         <v>31</v>
@@ -10580,7 +10580,7 @@
         <v>1483</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H13">
         <v>350000</v>
@@ -10612,16 +10612,16 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E14">
         <v>27</v>
@@ -10636,7 +10636,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J14">
         <v>92</v>
@@ -10662,16 +10662,16 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D15" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E15">
         <v>27</v>
@@ -10712,16 +10712,16 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D16" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E16">
         <v>22</v>
@@ -10762,16 +10762,16 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B17" t="s">
         <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D17" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E17">
         <v>30</v>
@@ -10809,16 +10809,16 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E18">
         <v>33</v>
@@ -10859,16 +10859,16 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D19" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E19">
         <v>25</v>
@@ -10880,7 +10880,7 @@
         <v>500000</v>
       </c>
       <c r="I19" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J19">
         <v>91.2</v>
@@ -10906,16 +10906,16 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D20" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E20">
         <v>27</v>
@@ -10924,13 +10924,13 @@
         <v>3542</v>
       </c>
       <c r="G20" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J20">
         <v>91.09999999999999</v>
@@ -10956,16 +10956,16 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B21" t="s">
         <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D21" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E21">
         <v>23</v>
@@ -11006,16 +11006,16 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D22" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E22">
         <v>32</v>
@@ -11024,13 +11024,13 @@
         <v>2595</v>
       </c>
       <c r="G22" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H22">
         <v>300000</v>
       </c>
       <c r="I22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J22">
         <v>90.90000000000001</v>
@@ -11056,16 +11056,16 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B23" t="s">
         <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D23" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -11074,7 +11074,7 @@
         <v>2098</v>
       </c>
       <c r="G23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -11106,16 +11106,16 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B24" t="s">
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D24" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E24">
         <v>27</v>
@@ -11124,13 +11124,13 @@
         <v>2761</v>
       </c>
       <c r="G24" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J24">
         <v>90.2</v>
@@ -11156,16 +11156,16 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D25" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E25">
         <v>32</v>
@@ -11174,13 +11174,13 @@
         <v>2106</v>
       </c>
       <c r="G25" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H25">
         <v>450000</v>
       </c>
       <c r="I25" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J25">
         <v>90.2</v>
@@ -11206,16 +11206,16 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B26" t="s">
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D26" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -11224,13 +11224,13 @@
         <v>2647</v>
       </c>
       <c r="G26" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H26">
         <v>300000</v>
       </c>
       <c r="I26" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J26">
         <v>90</v>
@@ -11313,16 +11313,16 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E2">
         <v>29</v>
@@ -11331,13 +11331,13 @@
         <v>1437</v>
       </c>
       <c r="G2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H2">
         <v>400000</v>
       </c>
       <c r="I2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J2">
         <v>94.40000000000001</v>
@@ -11360,16 +11360,16 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E3">
         <v>32</v>
@@ -11378,7 +11378,7 @@
         <v>2371</v>
       </c>
       <c r="G3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H3">
         <v>300000</v>
@@ -11407,16 +11407,16 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E4">
         <v>29</v>
@@ -11425,7 +11425,7 @@
         <v>2034</v>
       </c>
       <c r="G4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -11454,16 +11454,16 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B5" t="s">
         <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E5">
         <v>31</v>
@@ -11472,13 +11472,13 @@
         <v>1834</v>
       </c>
       <c r="G5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H5">
         <v>800000</v>
       </c>
       <c r="I5" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J5">
         <v>92.09999999999999</v>
@@ -11501,16 +11501,16 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B6" t="s">
         <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E6">
         <v>27</v>
@@ -11519,13 +11519,13 @@
         <v>3268</v>
       </c>
       <c r="G6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H6">
         <v>250000</v>
       </c>
       <c r="I6" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J6">
         <v>91.90000000000001</v>
@@ -11548,16 +11548,16 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B7" t="s">
         <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E7">
         <v>30</v>
@@ -11566,13 +11566,13 @@
         <v>1947</v>
       </c>
       <c r="G7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H7">
         <v>1000000</v>
       </c>
       <c r="I7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J7">
         <v>91.7</v>
@@ -11595,16 +11595,16 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B8" t="s">
         <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D8" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E8">
         <v>30</v>
@@ -11616,7 +11616,7 @@
         <v>200000</v>
       </c>
       <c r="I8" t="s">
-        <v>84</v>
+        <v>184</v>
       </c>
       <c r="J8">
         <v>91.09999999999999</v>
@@ -11639,16 +11639,16 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B9" t="s">
         <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E9">
         <v>24</v>
@@ -11686,16 +11686,16 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B10" t="s">
         <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E10">
         <v>27</v>
@@ -11733,16 +11733,16 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B11" t="s">
         <v>99</v>
       </c>
       <c r="C11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E11">
         <v>32</v>
@@ -11777,16 +11777,16 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B12" t="s">
         <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D12" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E12">
         <v>31</v>
@@ -11795,7 +11795,7 @@
         <v>2745</v>
       </c>
       <c r="G12" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -11824,16 +11824,16 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D13" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E13">
         <v>30</v>
@@ -11842,13 +11842,13 @@
         <v>2643</v>
       </c>
       <c r="G13" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H13">
         <v>300000</v>
       </c>
       <c r="I13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J13">
         <v>88.5</v>
@@ -11871,16 +11871,16 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B14" t="s">
         <v>99</v>
       </c>
       <c r="C14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E14">
         <v>28</v>
@@ -11895,7 +11895,7 @@
         <v>800000</v>
       </c>
       <c r="I14" t="s">
-        <v>84</v>
+        <v>184</v>
       </c>
       <c r="J14">
         <v>88.3</v>
@@ -11918,16 +11918,16 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B15" t="s">
         <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D15" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E15">
         <v>32</v>
@@ -11962,16 +11962,16 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D16" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E16">
         <v>32</v>
@@ -12006,16 +12006,16 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D17" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E17">
         <v>26</v>
@@ -12053,16 +12053,16 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B18" t="s">
         <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D18" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E18">
         <v>26</v>
@@ -12071,7 +12071,7 @@
         <v>1775</v>
       </c>
       <c r="G18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H18">
         <v>250000</v>
@@ -12100,16 +12100,16 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B19" t="s">
         <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D19" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E19">
         <v>31</v>
@@ -12118,13 +12118,13 @@
         <v>2806</v>
       </c>
       <c r="G19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H19">
         <v>1000000</v>
       </c>
       <c r="I19" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J19">
         <v>86.8</v>
@@ -12147,16 +12147,16 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D20" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E20">
         <v>25</v>
@@ -12194,16 +12194,16 @@
     </row>
     <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B21" t="s">
         <v>99</v>
       </c>
       <c r="C21" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D21" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E21">
         <v>32</v>
@@ -12218,7 +12218,7 @@
         <v>450000</v>
       </c>
       <c r="I21" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J21">
         <v>86.40000000000001</v>
@@ -12241,16 +12241,16 @@
     </row>
     <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B22" t="s">
         <v>99</v>
       </c>
       <c r="C22" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D22" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E22">
         <v>30</v>
@@ -12285,16 +12285,16 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D23" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E23">
         <v>29</v>
@@ -12332,16 +12332,16 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B24" t="s">
         <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D24" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E24">
         <v>30</v>
@@ -12379,16 +12379,16 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D25" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E25">
         <v>25</v>
@@ -12397,13 +12397,13 @@
         <v>1572</v>
       </c>
       <c r="G25" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J25">
         <v>85.09999999999999</v>
@@ -12426,16 +12426,16 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B26" t="s">
         <v>99</v>
       </c>
       <c r="C26" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D26" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E26">
         <v>23</v>
@@ -12444,7 +12444,7 @@
         <v>1794</v>
       </c>
       <c r="G26" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H26">
         <v>400000</v>

--- a/Santa Cruz V2/listas/bola_parada_especialistas.xlsx
+++ b/Santa Cruz V2/listas/bola_parada_especialistas.xlsx
@@ -1073,12 +1073,12 @@
     <t>Evander</t>
   </si>
   <si>
+    <t>J. Bartolo</t>
+  </si>
+  <si>
     <t>Arthur Rezende</t>
   </si>
   <si>
-    <t>J. Bartolo</t>
-  </si>
-  <si>
     <t>Valdívia</t>
   </si>
   <si>
@@ -1148,10 +1148,10 @@
     <t>Cincinnati</t>
   </si>
   <si>
+    <t>Asteras Tripolis</t>
+  </si>
+  <si>
     <t>Muharraq</t>
-  </si>
-  <si>
-    <t>Asteras Tripolis</t>
   </si>
   <si>
     <t>Jeonnam Dragons</t>
@@ -10421,10 +10421,10 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
         <v>350</v>
@@ -10433,45 +10433,48 @@
         <v>375</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F10">
-        <v>1839</v>
+        <v>2529</v>
+      </c>
+      <c r="G10" t="s">
+        <v>390</v>
       </c>
       <c r="H10">
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="I10" t="s">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="J10">
         <v>92.59999999999999</v>
       </c>
       <c r="K10">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="L10">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="M10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N10">
-        <v>22.2</v>
+        <v>37.5</v>
       </c>
       <c r="O10">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="P10">
-        <v>38.1</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
         <v>351</v>
@@ -10480,40 +10483,37 @@
         <v>376</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>2529</v>
-      </c>
-      <c r="G11" t="s">
-        <v>390</v>
+        <v>1839</v>
       </c>
       <c r="H11">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="I11" t="s">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="J11">
         <v>92.59999999999999</v>
       </c>
       <c r="K11">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="L11">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="M11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N11">
-        <v>37.5</v>
+        <v>22.2</v>
       </c>
       <c r="O11">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="P11">
-        <v>28.6</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="12" spans="1:16">
